--- a/data/source/weekly/cs-en-us-083pct.xlsx
+++ b/data/source/weekly/cs-en-us-083pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">7</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/2/2026</t>
+      <t xml:space="preserve">2/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/8/2026</t>
+      <t xml:space="preserve">2/15/2026</t>
     </r>
   </si>
   <si>
@@ -854,17 +854,17 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>21</v>
+      <c r="D14" s="14">
+        <v>1</v>
+      </c>
+      <c r="E14" s="15">
+        <v>-100</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G14" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H14" s="15">
         <v>-100</v>
@@ -873,7 +873,7 @@
         <v>20</v>
       </c>
       <c r="J14" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K14" s="15">
         <v>-100</v>
@@ -895,38 +895,38 @@
       <c r="C15" s="14">
         <v>1</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>0</v>
       </c>
       <c r="F15" s="14">
         <v>6</v>
       </c>
       <c r="G15" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H15" s="15">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I15" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J15" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K15" s="15">
-        <v>200</v>
+        <v>166.666666666667</v>
       </c>
       <c r="L15" s="15">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M15" s="15">
-        <v>100</v>
+        <v>166.666666666667</v>
       </c>
       <c r="N15" s="15">
-        <v>-14.285714285714</v>
+        <v>-33.333333333333</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D16" s="14">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E16" s="15">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="F16" s="14">
+        <v>22</v>
+      </c>
+      <c r="G16" s="14">
+        <v>14</v>
+      </c>
+      <c r="H16" s="15">
+        <v>57.142857142857</v>
+      </c>
+      <c r="I16" s="14">
+        <v>37</v>
+      </c>
+      <c r="J16" s="14">
         <v>18</v>
       </c>
-      <c r="G16" s="14">
-        <v>10</v>
-      </c>
-      <c r="H16" s="15">
-        <v>80</v>
-      </c>
-      <c r="I16" s="14">
-        <v>29</v>
-      </c>
-      <c r="J16" s="14">
-        <v>11</v>
-      </c>
       <c r="K16" s="15">
-        <v>163.636363636364</v>
+        <v>105.555555555556</v>
       </c>
       <c r="L16" s="15">
-        <v>-27.5</v>
+        <v>-21.276595744680</v>
       </c>
       <c r="M16" s="15">
-        <v>-43.137254901960</v>
+        <v>-37.288135593220</v>
       </c>
       <c r="N16" s="15">
-        <v>-81.761006289308</v>
+        <v>-79.891304347826</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D17" s="14">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E17" s="15">
-        <v>-50</v>
+        <v>133.333333333333</v>
       </c>
       <c r="F17" s="14">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="G17" s="14">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="H17" s="15">
-        <v>-3.225806451612</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="I17" s="14">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J17" s="14">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K17" s="15">
-        <v>10.526315789473</v>
+        <v>17.073170731707</v>
       </c>
       <c r="L17" s="15">
-        <v>-2.325581395348</v>
+        <v>-5.882352941176</v>
       </c>
       <c r="M17" s="15">
-        <v>55.555555555555</v>
+        <v>54.838709677419</v>
       </c>
       <c r="N17" s="15">
-        <v>-51.162790697674</v>
+        <v>-52.475247524752</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,37 +1019,37 @@
         <v>3</v>
       </c>
       <c r="D18" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18" s="15">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="F18" s="14">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G18" s="14">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H18" s="15">
-        <v>66.666666666666</v>
+        <v>70</v>
       </c>
       <c r="I18" s="14">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J18" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K18" s="15">
-        <v>52.941176470588</v>
+        <v>61.111111111111</v>
       </c>
       <c r="L18" s="15">
-        <v>-25.714285714285</v>
+        <v>-29.268292682926</v>
       </c>
       <c r="M18" s="15">
-        <v>-31.578947368421</v>
+        <v>-30.952380952381</v>
       </c>
       <c r="N18" s="15">
-        <v>-82.191780821917</v>
+        <v>-82.424242424242</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D19" s="14">
         <v>13</v>
       </c>
       <c r="E19" s="15">
-        <v>-7.692307692307</v>
+        <v>0</v>
       </c>
       <c r="F19" s="14">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="G19" s="14">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="H19" s="15">
-        <v>54.054054054054</v>
+        <v>9.090909090909</v>
       </c>
       <c r="I19" s="14">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="J19" s="14">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="K19" s="15">
-        <v>50</v>
+        <v>38.461538461538</v>
       </c>
       <c r="L19" s="15">
-        <v>39.285714285714</v>
+        <v>36.363636363636</v>
       </c>
       <c r="M19" s="15">
-        <v>129.411764705882</v>
+        <v>130.769230769231</v>
       </c>
       <c r="N19" s="15">
-        <v>41.818181818181</v>
+        <v>47.540983606557</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D20" s="14">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E20" s="15">
-        <v>0</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="F20" s="14">
         <v>10</v>
       </c>
       <c r="G20" s="14">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H20" s="15">
-        <v>66.666666666666</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="I20" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J20" s="14">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="K20" s="15">
-        <v>66.666666666666</v>
+        <v>0</v>
       </c>
       <c r="L20" s="15">
-        <v>-31.818181818181</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="M20" s="15">
-        <v>7.142857142857</v>
+        <v>6.666666666666</v>
       </c>
       <c r="N20" s="15">
-        <v>-86.607142857142</v>
+        <v>-87.969924812030</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,72 +1139,72 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D21" s="17">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="E21" s="18">
         <v>0</v>
       </c>
       <c r="F21" s="17">
-        <v>141</v>
+        <v>125</v>
       </c>
       <c r="G21" s="17">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="H21" s="18">
-        <v>42.424242424242</v>
+        <v>15.740740740740</v>
       </c>
       <c r="I21" s="17">
-        <v>196</v>
+        <v>228</v>
       </c>
       <c r="J21" s="17">
-        <v>130</v>
+        <v>163</v>
       </c>
       <c r="K21" s="18">
-        <v>50.769230769230</v>
+        <v>39.877300613496</v>
       </c>
       <c r="L21" s="18">
-        <v>-2</v>
+        <v>-2.978723404255</v>
       </c>
       <c r="M21" s="18">
-        <v>17.365269461077</v>
+        <v>20.634920634920</v>
       </c>
       <c r="N21" s="18">
-        <v>-65.794066317626</v>
+        <v>-65.662650602409</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
+      <c r="C22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="14">
         <v>2</v>
       </c>
-      <c r="D22" s="14">
-        <v>1</v>
-      </c>
       <c r="E22" s="15">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="F22" s="14">
         <v>2</v>
       </c>
       <c r="G22" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H22" s="15">
-        <v>100</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I22" s="14">
         <v>3</v>
       </c>
       <c r="J22" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K22" s="15">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="L22" s="15">
         <v>-50</v>
@@ -1220,32 +1220,32 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="14">
+      <c r="C23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" s="14">
         <v>1</v>
       </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
+      <c r="E23" s="15">
+        <v>-100</v>
       </c>
       <c r="F23" s="14">
         <v>3</v>
       </c>
       <c r="G23" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H23" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I23" s="14">
         <v>4</v>
       </c>
       <c r="J23" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K23" s="15">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="L23" s="15">
         <v>-33.333333333333</v>
@@ -1265,34 +1265,34 @@
         <v>15</v>
       </c>
       <c r="D24" s="14">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E24" s="15">
-        <v>-11.764705882352</v>
+        <v>-48.275862068965</v>
       </c>
       <c r="F24" s="14">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G24" s="14">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H24" s="15">
-        <v>15</v>
+        <v>1.265822784810</v>
       </c>
       <c r="I24" s="14">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="J24" s="14">
-        <v>110</v>
+        <v>139</v>
       </c>
       <c r="K24" s="15">
-        <v>4.545454545454</v>
+        <v>-6.474820143884</v>
       </c>
       <c r="L24" s="15">
-        <v>19.791666666666</v>
+        <v>9.243697478991</v>
       </c>
       <c r="M24" s="15">
-        <v>69.117647058823</v>
+        <v>73.333333333333</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D25" s="14">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E25" s="15">
+        <v>-75</v>
+      </c>
+      <c r="F25" s="14">
+        <v>14</v>
+      </c>
+      <c r="G25" s="14">
+        <v>20</v>
+      </c>
+      <c r="H25" s="15">
+        <v>-30</v>
+      </c>
+      <c r="I25" s="14">
+        <v>24</v>
+      </c>
+      <c r="J25" s="14">
+        <v>31</v>
+      </c>
+      <c r="K25" s="15">
+        <v>-22.580645161290</v>
+      </c>
+      <c r="L25" s="15">
         <v>0</v>
-      </c>
-      <c r="F25" s="14">
-        <v>17</v>
-      </c>
-      <c r="G25" s="14">
-        <v>15</v>
-      </c>
-      <c r="H25" s="15">
-        <v>13.333333333333</v>
-      </c>
-      <c r="I25" s="14">
-        <v>22</v>
-      </c>
-      <c r="J25" s="14">
-        <v>23</v>
-      </c>
-      <c r="K25" s="15">
-        <v>-4.347826086956</v>
-      </c>
-      <c r="L25" s="15">
-        <v>37.5</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D26" s="14">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E26" s="15">
-        <v>16.666666666666</v>
+        <v>22.222222222222</v>
       </c>
       <c r="F26" s="14">
         <v>49</v>
       </c>
       <c r="G26" s="14">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H26" s="15">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="I26" s="14">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="J26" s="14">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="K26" s="15">
-        <v>-7.042253521126</v>
+        <v>-1.25</v>
       </c>
       <c r="L26" s="15">
-        <v>0</v>
+        <v>2.597402597402</v>
       </c>
       <c r="M26" s="15">
-        <v>6.451612903225</v>
+        <v>-1.25</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,32 +1387,32 @@
       <c r="C27" s="14">
         <v>1</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
+        <v>0</v>
       </c>
       <c r="F27" s="14">
         <v>6</v>
       </c>
       <c r="G27" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H27" s="15">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I27" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J27" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K27" s="15">
-        <v>200</v>
+        <v>166.666666666667</v>
       </c>
       <c r="L27" s="15">
-        <v>-14.285714285714</v>
+        <v>14.285714285714</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="14">
+        <v>2</v>
       </c>
       <c r="D28" s="14">
         <v>1</v>
       </c>
       <c r="E28" s="15">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="F28" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G28" s="14">
         <v>5</v>
       </c>
       <c r="H28" s="15">
-        <v>-40</v>
+        <v>-20</v>
       </c>
       <c r="I28" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J28" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K28" s="15">
-        <v>-28.571428571428</v>
+        <v>-25</v>
       </c>
       <c r="L28" s="15">
-        <v>-16.666666666666</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,29 +1469,29 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="D29" s="14">
+        <v>1</v>
+      </c>
+      <c r="E29" s="15">
+        <v>-100</v>
       </c>
       <c r="F29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H29" s="13" t="s">
-        <v>21</v>
+      <c r="G29" s="14">
+        <v>1</v>
+      </c>
+      <c r="H29" s="15">
+        <v>-100</v>
       </c>
       <c r="I29" s="14">
         <v>1</v>
       </c>
-      <c r="J29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K29" s="13" t="s">
-        <v>21</v>
+      <c r="J29" s="14">
+        <v>1</v>
+      </c>
+      <c r="K29" s="15">
+        <v>0</v>
       </c>
       <c r="L29" s="13" t="s">
         <v>21</v>
@@ -1500,7 +1500,7 @@
         <v>-50</v>
       </c>
       <c r="N29" s="15">
-        <v>-96.428571428571</v>
+        <v>-96.875</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1510,29 +1510,29 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="D30" s="14">
+        <v>1</v>
+      </c>
+      <c r="E30" s="15">
+        <v>-100</v>
       </c>
       <c r="F30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H30" s="13" t="s">
-        <v>21</v>
+      <c r="G30" s="14">
+        <v>1</v>
+      </c>
+      <c r="H30" s="15">
+        <v>-100</v>
       </c>
       <c r="I30" s="14">
         <v>1</v>
       </c>
-      <c r="J30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K30" s="13" t="s">
-        <v>21</v>
+      <c r="J30" s="14">
+        <v>1</v>
+      </c>
+      <c r="K30" s="15">
+        <v>0</v>
       </c>
       <c r="L30" s="13" t="s">
         <v>21</v>
@@ -1541,7 +1541,7 @@
         <v>-50</v>
       </c>
       <c r="N30" s="15">
-        <v>-96.428571428571</v>
+        <v>-96.875</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1557,8 +1557,8 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="14">
-        <v>2</v>
+      <c r="F31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
@@ -1567,7 +1567,7 @@
         <v>21</v>
       </c>
       <c r="I31" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J31" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-083pct.xlsx
+++ b/data/source/weekly/cs-en-us-083pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t xml:space="preserve">8</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/9/2026</t>
+      <t xml:space="preserve">2/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/15/2026</t>
+      <t xml:space="preserve">2/22/2026</t>
     </r>
   </si>
   <si>
@@ -854,17 +854,17 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="14">
+      <c r="D14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G14" s="14">
         <v>1</v>
-      </c>
-      <c r="E14" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G14" s="14">
-        <v>2</v>
       </c>
       <c r="H14" s="15">
         <v>-100</v>
@@ -881,8 +881,8 @@
       <c r="L14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="M14" s="13" t="s">
-        <v>21</v>
+      <c r="M14" s="15">
+        <v>-100</v>
       </c>
       <c r="N14" s="15">
         <v>-100</v>
@@ -892,32 +892,32 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>1</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F15" s="14">
+        <v>4</v>
+      </c>
+      <c r="G15" s="14">
+        <v>4</v>
+      </c>
+      <c r="H15" s="15">
         <v>0</v>
-      </c>
-      <c r="F15" s="14">
-        <v>6</v>
-      </c>
-      <c r="G15" s="14">
-        <v>3</v>
-      </c>
-      <c r="H15" s="15">
-        <v>100</v>
       </c>
       <c r="I15" s="14">
         <v>8</v>
       </c>
       <c r="J15" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K15" s="15">
-        <v>166.666666666667</v>
+        <v>60</v>
       </c>
       <c r="L15" s="15">
         <v>100</v>
@@ -926,7 +926,7 @@
         <v>166.666666666667</v>
       </c>
       <c r="N15" s="15">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D16" s="14">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E16" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F16" s="14">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G16" s="14">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H16" s="15">
-        <v>57.142857142857</v>
+        <v>25</v>
       </c>
       <c r="I16" s="14">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="J16" s="14">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K16" s="15">
-        <v>105.555555555556</v>
+        <v>100</v>
       </c>
       <c r="L16" s="15">
-        <v>-21.276595744680</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="M16" s="15">
-        <v>-37.288135593220</v>
+        <v>-35.483870967741</v>
       </c>
       <c r="N16" s="15">
-        <v>-79.891304347826</v>
+        <v>-80.099502487562</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
+        <v>6</v>
+      </c>
+      <c r="D17" s="14">
         <v>7</v>
       </c>
-      <c r="D17" s="14">
-        <v>3</v>
-      </c>
       <c r="E17" s="15">
-        <v>133.333333333333</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="F17" s="14">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G17" s="14">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H17" s="15">
-        <v>-8.333333333333</v>
+        <v>8.695652173913</v>
       </c>
       <c r="I17" s="14">
+        <v>54</v>
+      </c>
+      <c r="J17" s="14">
         <v>48</v>
       </c>
-      <c r="J17" s="14">
-        <v>41</v>
-      </c>
       <c r="K17" s="15">
-        <v>17.073170731707</v>
+        <v>12.5</v>
       </c>
       <c r="L17" s="15">
-        <v>-5.882352941176</v>
+        <v>-6.896551724137</v>
       </c>
       <c r="M17" s="15">
-        <v>54.838709677419</v>
+        <v>58.823529411764</v>
       </c>
       <c r="N17" s="15">
-        <v>-52.475247524752</v>
+        <v>-51.785714285714</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D18" s="14">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E18" s="15">
-        <v>200</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F18" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G18" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H18" s="15">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="I18" s="14">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="J18" s="14">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="K18" s="15">
-        <v>61.111111111111</v>
+        <v>41.666666666666</v>
       </c>
       <c r="L18" s="15">
-        <v>-29.268292682926</v>
+        <v>-24.444444444444</v>
       </c>
       <c r="M18" s="15">
-        <v>-30.952380952381</v>
+        <v>-27.659574468085</v>
       </c>
       <c r="N18" s="15">
-        <v>-82.424242424242</v>
+        <v>-82.474226804123</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D19" s="14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E19" s="15">
-        <v>0</v>
+        <v>16.666666666666</v>
       </c>
       <c r="F19" s="14">
         <v>48</v>
       </c>
       <c r="G19" s="14">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="H19" s="15">
-        <v>9.090909090909</v>
+        <v>-4</v>
       </c>
       <c r="I19" s="14">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="J19" s="14">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="K19" s="15">
-        <v>38.461538461538</v>
+        <v>33.766233766233</v>
       </c>
       <c r="L19" s="15">
-        <v>36.363636363636</v>
+        <v>22.619047619047</v>
       </c>
       <c r="M19" s="15">
-        <v>130.769230769231</v>
+        <v>139.53488372093</v>
       </c>
       <c r="N19" s="15">
-        <v>47.540983606557</v>
+        <v>47.142857142857</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,37 +1101,37 @@
         <v>2</v>
       </c>
       <c r="D20" s="14">
+        <v>4</v>
+      </c>
+      <c r="E20" s="15">
+        <v>-50</v>
+      </c>
+      <c r="F20" s="14">
         <v>7</v>
       </c>
-      <c r="E20" s="15">
-        <v>-71.428571428571</v>
-      </c>
-      <c r="F20" s="14">
-        <v>10</v>
-      </c>
       <c r="G20" s="14">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H20" s="15">
-        <v>-9.090909090909</v>
+        <v>-50</v>
       </c>
       <c r="I20" s="14">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J20" s="14">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="K20" s="15">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="L20" s="15">
-        <v>-38.461538461538</v>
+        <v>-37.931034482758</v>
       </c>
       <c r="M20" s="15">
-        <v>6.666666666666</v>
+        <v>5.882352941176</v>
       </c>
       <c r="N20" s="15">
-        <v>-87.969924812030</v>
+        <v>-87.755102040816</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D21" s="17">
         <v>33</v>
       </c>
       <c r="E21" s="18">
-        <v>0</v>
+        <v>-12.121212121212</v>
       </c>
       <c r="F21" s="17">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="G21" s="17">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="H21" s="18">
-        <v>15.740740740740</v>
+        <v>1.666666666666</v>
       </c>
       <c r="I21" s="17">
-        <v>228</v>
+        <v>257</v>
       </c>
       <c r="J21" s="17">
-        <v>163</v>
+        <v>196</v>
       </c>
       <c r="K21" s="18">
-        <v>39.877300613496</v>
+        <v>31.122448979591</v>
       </c>
       <c r="L21" s="18">
-        <v>-2.978723404255</v>
+        <v>-6.884057971014</v>
       </c>
       <c r="M21" s="18">
-        <v>20.634920634920</v>
+        <v>24.154589371980</v>
       </c>
       <c r="N21" s="18">
-        <v>-65.662650602409</v>
+        <v>-65.733333333333</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,11 +1182,11 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="14">
-        <v>2</v>
-      </c>
-      <c r="E22" s="15">
-        <v>-100</v>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="14">
         <v>2</v>
@@ -1207,7 +1207,7 @@
         <v>0</v>
       </c>
       <c r="L22" s="15">
-        <v>-50</v>
+        <v>-62.5</v>
       </c>
       <c r="M22" s="15">
         <v>-50</v>
@@ -1223,20 +1223,20 @@
       <c r="C23" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D23" s="14">
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F23" s="14">
         <v>1</v>
-      </c>
-      <c r="E23" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F23" s="14">
-        <v>3</v>
       </c>
       <c r="G23" s="14">
         <v>2</v>
       </c>
       <c r="H23" s="15">
-        <v>50</v>
+        <v>-50</v>
       </c>
       <c r="I23" s="14">
         <v>4</v>
@@ -1248,7 +1248,7 @@
         <v>-20</v>
       </c>
       <c r="L23" s="15">
-        <v>-33.333333333333</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="M23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="D24" s="14">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="E24" s="15">
-        <v>-48.275862068965</v>
+        <v>64.285714285714</v>
       </c>
       <c r="F24" s="14">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="G24" s="14">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H24" s="15">
-        <v>1.265822784810</v>
+        <v>-9.333333333333</v>
       </c>
       <c r="I24" s="14">
-        <v>130</v>
+        <v>152</v>
       </c>
       <c r="J24" s="14">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="K24" s="15">
-        <v>-6.474820143884</v>
+        <v>-0.653594771241</v>
       </c>
       <c r="L24" s="15">
-        <v>9.243697478991</v>
+        <v>11.764705882352</v>
       </c>
       <c r="M24" s="15">
-        <v>73.333333333333</v>
+        <v>74.712643678160</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,31 +1306,31 @@
         <v>2</v>
       </c>
       <c r="D25" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E25" s="15">
-        <v>-75</v>
+        <v>-60</v>
       </c>
       <c r="F25" s="14">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="G25" s="14">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H25" s="15">
-        <v>-30</v>
+        <v>-60.869565217391</v>
       </c>
       <c r="I25" s="14">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J25" s="14">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="K25" s="15">
-        <v>-22.580645161290</v>
+        <v>-27.777777777777</v>
       </c>
       <c r="L25" s="15">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D26" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E26" s="15">
-        <v>22.222222222222</v>
+        <v>75</v>
       </c>
       <c r="F26" s="14">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="G26" s="14">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="H26" s="15">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="I26" s="14">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="J26" s="14">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="K26" s="15">
-        <v>-1.25</v>
+        <v>4.545454545454</v>
       </c>
       <c r="L26" s="15">
-        <v>2.597402597402</v>
+        <v>3.370786516853</v>
       </c>
       <c r="M26" s="15">
-        <v>-1.25</v>
+        <v>-8</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,32 +1384,32 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>1</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F27" s="14">
+        <v>4</v>
+      </c>
+      <c r="G27" s="14">
+        <v>4</v>
+      </c>
+      <c r="H27" s="15">
         <v>0</v>
-      </c>
-      <c r="F27" s="14">
-        <v>6</v>
-      </c>
-      <c r="G27" s="14">
-        <v>3</v>
-      </c>
-      <c r="H27" s="15">
-        <v>100</v>
       </c>
       <c r="I27" s="14">
         <v>8</v>
       </c>
       <c r="J27" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K27" s="15">
-        <v>166.666666666667</v>
+        <v>60</v>
       </c>
       <c r="L27" s="15">
         <v>14.285714285714</v>
@@ -1435,25 +1435,25 @@
         <v>100</v>
       </c>
       <c r="F28" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G28" s="14">
         <v>5</v>
       </c>
       <c r="H28" s="15">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="I28" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J28" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K28" s="15">
-        <v>-25</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="L28" s="15">
-        <v>-14.285714285714</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,11 +1469,11 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="14">
-        <v>1</v>
-      </c>
-      <c r="E29" s="15">
-        <v>-100</v>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F29" s="13" t="s">
         <v>20</v>
@@ -1500,7 +1500,7 @@
         <v>-50</v>
       </c>
       <c r="N29" s="15">
-        <v>-96.875</v>
+        <v>-97.297297297297</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1510,11 +1510,11 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="14">
-        <v>1</v>
-      </c>
-      <c r="E30" s="15">
-        <v>-100</v>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F30" s="13" t="s">
         <v>20</v>
@@ -1541,7 +1541,7 @@
         <v>-50</v>
       </c>
       <c r="N30" s="15">
-        <v>-96.875</v>
+        <v>-97.297297297297</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-083pct.xlsx
+++ b/data/source/weekly/cs-en-us-083pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">8</t>
+      <t xml:space="preserve">9</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/16/2026</t>
+      <t xml:space="preserve">2/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/22/2026</t>
+      <t xml:space="preserve">3/1/2026</t>
     </r>
   </si>
   <si>
@@ -892,41 +892,41 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="14">
-        <v>2</v>
-      </c>
-      <c r="E15" s="15">
-        <v>-100</v>
+      <c r="C15" s="14">
+        <v>1</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G15" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H15" s="15">
         <v>0</v>
       </c>
       <c r="I15" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J15" s="14">
         <v>5</v>
       </c>
       <c r="K15" s="15">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="L15" s="15">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="M15" s="15">
-        <v>166.666666666667</v>
+        <v>80</v>
       </c>
       <c r="N15" s="15">
-        <v>-50</v>
+        <v>-43.75</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D16" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16" s="15">
-        <v>50</v>
+        <v>800</v>
       </c>
       <c r="F16" s="14">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G16" s="14">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H16" s="15">
-        <v>25</v>
+        <v>118.181818181818</v>
       </c>
       <c r="I16" s="14">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="J16" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K16" s="15">
-        <v>100</v>
+        <v>133.333333333333</v>
       </c>
       <c r="L16" s="15">
-        <v>-28.571428571428</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="M16" s="15">
-        <v>-35.483870967741</v>
+        <v>-23.4375</v>
       </c>
       <c r="N16" s="15">
-        <v>-80.099502487562</v>
+        <v>-77.927927927927</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D17" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E17" s="15">
-        <v>-14.285714285714</v>
+        <v>0</v>
       </c>
       <c r="F17" s="14">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G17" s="14">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="H17" s="15">
-        <v>8.695652173913</v>
+        <v>0</v>
       </c>
       <c r="I17" s="14">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="J17" s="14">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="K17" s="15">
         <v>12.5</v>
       </c>
       <c r="L17" s="15">
-        <v>-6.896551724137</v>
+        <v>-3.076923076923</v>
       </c>
       <c r="M17" s="15">
-        <v>58.823529411764</v>
+        <v>80</v>
       </c>
       <c r="N17" s="15">
-        <v>-51.785714285714</v>
+        <v>-51.162790697674</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,13 +1016,13 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D18" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E18" s="15">
-        <v>-33.333333333333</v>
+        <v>100</v>
       </c>
       <c r="F18" s="14">
         <v>18</v>
@@ -1034,22 +1034,22 @@
         <v>50</v>
       </c>
       <c r="I18" s="14">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="J18" s="14">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K18" s="15">
-        <v>41.666666666666</v>
+        <v>51.851851851851</v>
       </c>
       <c r="L18" s="15">
-        <v>-24.444444444444</v>
+        <v>-18</v>
       </c>
       <c r="M18" s="15">
-        <v>-27.659574468085</v>
+        <v>-22.641509433962</v>
       </c>
       <c r="N18" s="15">
-        <v>-82.474226804123</v>
+        <v>-80.930232558139</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
+        <v>13</v>
+      </c>
+      <c r="D19" s="14">
         <v>14</v>
       </c>
-      <c r="D19" s="14">
-        <v>12</v>
-      </c>
       <c r="E19" s="15">
-        <v>16.666666666666</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="F19" s="14">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G19" s="14">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H19" s="15">
-        <v>-4</v>
+        <v>-3.846153846153</v>
       </c>
       <c r="I19" s="14">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="J19" s="14">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="K19" s="15">
-        <v>33.766233766233</v>
+        <v>26.373626373626</v>
       </c>
       <c r="L19" s="15">
-        <v>22.619047619047</v>
+        <v>21.052631578947</v>
       </c>
       <c r="M19" s="15">
-        <v>139.53488372093</v>
+        <v>144.68085106383</v>
       </c>
       <c r="N19" s="15">
-        <v>47.142857142857</v>
+        <v>55.405405405405</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="14">
-        <v>2</v>
+      <c r="C20" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D20" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E20" s="15">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="F20" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G20" s="14">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H20" s="15">
-        <v>-50</v>
+        <v>-64.705882352941</v>
       </c>
       <c r="I20" s="14">
         <v>18</v>
       </c>
       <c r="J20" s="14">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K20" s="15">
+        <v>-21.739130434782</v>
+      </c>
+      <c r="L20" s="15">
+        <v>-43.75</v>
+      </c>
+      <c r="M20" s="15">
         <v>-10</v>
       </c>
-      <c r="L20" s="15">
-        <v>-37.931034482758</v>
-      </c>
-      <c r="M20" s="15">
-        <v>5.882352941176</v>
-      </c>
       <c r="N20" s="15">
-        <v>-87.755102040816</v>
+        <v>-89.285714285714</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
+        <v>37</v>
+      </c>
+      <c r="D21" s="17">
         <v>29</v>
       </c>
-      <c r="D21" s="17">
-        <v>33</v>
-      </c>
       <c r="E21" s="18">
-        <v>-12.121212121212</v>
+        <v>27.586206896551</v>
       </c>
       <c r="F21" s="17">
+        <v>127</v>
+      </c>
+      <c r="G21" s="17">
         <v>122</v>
       </c>
-      <c r="G21" s="17">
-        <v>120</v>
-      </c>
       <c r="H21" s="18">
-        <v>1.666666666666</v>
+        <v>4.098360655737</v>
       </c>
       <c r="I21" s="17">
-        <v>257</v>
+        <v>295</v>
       </c>
       <c r="J21" s="17">
-        <v>196</v>
+        <v>225</v>
       </c>
       <c r="K21" s="18">
-        <v>31.122448979591</v>
+        <v>31.111111111111</v>
       </c>
       <c r="L21" s="18">
-        <v>-6.884057971014</v>
+        <v>-4.530744336569</v>
       </c>
       <c r="M21" s="18">
-        <v>24.154589371980</v>
+        <v>31.111111111111</v>
       </c>
       <c r="N21" s="18">
-        <v>-65.733333333333</v>
+        <v>-64.628297362110</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="14">
+        <v>2</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1189,28 +1189,28 @@
         <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G22" s="14">
         <v>3</v>
       </c>
       <c r="H22" s="15">
-        <v>-33.333333333333</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I22" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J22" s="14">
         <v>3</v>
       </c>
       <c r="K22" s="15">
-        <v>0</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L22" s="15">
-        <v>-62.5</v>
+        <v>-37.5</v>
       </c>
       <c r="M22" s="15">
-        <v>-50</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,35 +1220,35 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
+      <c r="C23" s="14">
+        <v>2</v>
+      </c>
+      <c r="D23" s="14">
+        <v>1</v>
+      </c>
+      <c r="E23" s="15">
+        <v>100</v>
       </c>
       <c r="F23" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G23" s="14">
         <v>2</v>
       </c>
       <c r="H23" s="15">
-        <v>-50</v>
+        <v>50</v>
       </c>
       <c r="I23" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J23" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K23" s="15">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="L23" s="15">
-        <v>-42.857142857142</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="M23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D24" s="14">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E24" s="15">
-        <v>64.285714285714</v>
+        <v>0</v>
       </c>
       <c r="F24" s="14">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G24" s="14">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H24" s="15">
-        <v>-9.333333333333</v>
+        <v>-12.987012987013</v>
       </c>
       <c r="I24" s="14">
-        <v>152</v>
+        <v>167</v>
       </c>
       <c r="J24" s="14">
-        <v>153</v>
+        <v>170</v>
       </c>
       <c r="K24" s="15">
-        <v>-0.653594771241</v>
+        <v>-1.764705882352</v>
       </c>
       <c r="L24" s="15">
-        <v>11.764705882352</v>
+        <v>0.602409638554</v>
       </c>
       <c r="M24" s="15">
-        <v>74.712643678160</v>
+        <v>62.135922330097</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D25" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E25" s="15">
-        <v>-60</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F25" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G25" s="14">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="H25" s="15">
-        <v>-60.869565217391</v>
+        <v>-36.842105263157</v>
       </c>
       <c r="I25" s="14">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="J25" s="14">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K25" s="15">
-        <v>-27.777777777777</v>
+        <v>-20.512820512820</v>
       </c>
       <c r="L25" s="15">
-        <v>4</v>
+        <v>-8.823529411764</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D26" s="14">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E26" s="15">
-        <v>75</v>
+        <v>-50</v>
       </c>
       <c r="F26" s="14">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="G26" s="14">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="H26" s="15">
-        <v>35</v>
+        <v>4.255319148936</v>
       </c>
       <c r="I26" s="14">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="J26" s="14">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="K26" s="15">
-        <v>4.545454545454</v>
+        <v>-4.716981132075</v>
       </c>
       <c r="L26" s="15">
-        <v>3.370786516853</v>
+        <v>3.061224489795</v>
       </c>
       <c r="M26" s="15">
-        <v>-8</v>
+        <v>-9.009009009009</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="14">
+      <c r="C27" s="14">
         <v>2</v>
       </c>
-      <c r="E27" s="15">
-        <v>-100</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="14">
         <v>4</v>
       </c>
       <c r="G27" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H27" s="15">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I27" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J27" s="14">
         <v>5</v>
       </c>
       <c r="K27" s="15">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="L27" s="15">
-        <v>14.285714285714</v>
+        <v>42.857142857142</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>2</v>
-      </c>
-      <c r="D28" s="14">
         <v>1</v>
       </c>
-      <c r="E28" s="15">
-        <v>100</v>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
         <v>5</v>
       </c>
       <c r="G28" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H28" s="15">
-        <v>0</v>
+        <v>66.666666666666</v>
       </c>
       <c r="I28" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J28" s="14">
         <v>9</v>
       </c>
       <c r="K28" s="15">
-        <v>-11.111111111111</v>
+        <v>0</v>
       </c>
       <c r="L28" s="15">
-        <v>-11.111111111111</v>
+        <v>-10</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,17 +1469,17 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="D29" s="14">
+        <v>1</v>
+      </c>
+      <c r="E29" s="15">
+        <v>-100</v>
       </c>
       <c r="F29" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H29" s="15">
         <v>-100</v>
@@ -1488,19 +1488,19 @@
         <v>1</v>
       </c>
       <c r="J29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K29" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="L29" s="13" t="s">
         <v>21</v>
       </c>
       <c r="M29" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N29" s="15">
-        <v>-97.297297297297</v>
+        <v>-97.560975609756</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1510,17 +1510,17 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="D30" s="14">
+        <v>1</v>
+      </c>
+      <c r="E30" s="15">
+        <v>-100</v>
       </c>
       <c r="F30" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H30" s="15">
         <v>-100</v>
@@ -1529,19 +1529,19 @@
         <v>1</v>
       </c>
       <c r="J30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K30" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="L30" s="13" t="s">
         <v>21</v>
       </c>
       <c r="M30" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N30" s="15">
-        <v>-97.297297297297</v>
+        <v>-97.560975609756</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-083pct.xlsx
+++ b/data/source/weekly/cs-en-us-083pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">9</t>
+      <t xml:space="preserve">10</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/23/2026</t>
+      <t xml:space="preserve">3/2/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/1/2026</t>
+      <t xml:space="preserve">3/8/2026</t>
     </r>
   </si>
   <si>
@@ -854,17 +854,17 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>21</v>
+      <c r="D14" s="14">
+        <v>1</v>
+      </c>
+      <c r="E14" s="15">
+        <v>-100</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G14" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H14" s="15">
         <v>-100</v>
@@ -873,7 +873,7 @@
         <v>20</v>
       </c>
       <c r="J14" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K14" s="15">
         <v>-100</v>
@@ -902,13 +902,13 @@
         <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G15" s="14">
         <v>3</v>
       </c>
       <c r="H15" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I15" s="14">
         <v>9</v>
@@ -920,13 +920,13 @@
         <v>80</v>
       </c>
       <c r="L15" s="15">
-        <v>125</v>
+        <v>50</v>
       </c>
       <c r="M15" s="15">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="N15" s="15">
-        <v>-43.75</v>
+        <v>-47.058823529411</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D16" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E16" s="15">
-        <v>800</v>
+        <v>100</v>
       </c>
       <c r="F16" s="14">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G16" s="14">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H16" s="15">
-        <v>118.181818181818</v>
+        <v>85.714285714285</v>
       </c>
       <c r="I16" s="14">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="J16" s="14">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K16" s="15">
-        <v>133.333333333333</v>
+        <v>124</v>
       </c>
       <c r="L16" s="15">
-        <v>-22.222222222222</v>
+        <v>-17.647058823529</v>
       </c>
       <c r="M16" s="15">
-        <v>-23.4375</v>
+        <v>-18.840579710144</v>
       </c>
       <c r="N16" s="15">
-        <v>-77.927927927927</v>
+        <v>-77.327935222672</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D17" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E17" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F17" s="14">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="G17" s="14">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H17" s="15">
-        <v>0</v>
+        <v>29.166666666666</v>
       </c>
       <c r="I17" s="14">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="J17" s="14">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="K17" s="15">
-        <v>12.5</v>
+        <v>16.129032258064</v>
       </c>
       <c r="L17" s="15">
-        <v>-3.076923076923</v>
+        <v>1.408450704225</v>
       </c>
       <c r="M17" s="15">
-        <v>80</v>
+        <v>75.609756097561</v>
       </c>
       <c r="N17" s="15">
-        <v>-51.162790697674</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,13 +1016,13 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D18" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E18" s="15">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="F18" s="14">
         <v>18</v>
@@ -1034,22 +1034,22 @@
         <v>50</v>
       </c>
       <c r="I18" s="14">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="J18" s="14">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K18" s="15">
-        <v>51.851851851851</v>
+        <v>55.172413793103</v>
       </c>
       <c r="L18" s="15">
-        <v>-18</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="M18" s="15">
-        <v>-22.641509433962</v>
+        <v>-22.413793103448</v>
       </c>
       <c r="N18" s="15">
-        <v>-80.930232558139</v>
+        <v>-81.481481481481</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D19" s="14">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E19" s="15">
-        <v>-7.142857142857</v>
+        <v>10</v>
       </c>
       <c r="F19" s="14">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G19" s="14">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H19" s="15">
-        <v>-3.846153846153</v>
+        <v>0</v>
       </c>
       <c r="I19" s="14">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="J19" s="14">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="K19" s="15">
-        <v>26.373626373626</v>
+        <v>23.762376237623</v>
       </c>
       <c r="L19" s="15">
-        <v>21.052631578947</v>
+        <v>15.740740740740</v>
       </c>
       <c r="M19" s="15">
-        <v>144.68085106383</v>
+        <v>135.849056603774</v>
       </c>
       <c r="N19" s="15">
-        <v>55.405405405405</v>
+        <v>48.809523809523</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
+      <c r="C20" s="14">
+        <v>1</v>
       </c>
       <c r="D20" s="14">
         <v>3</v>
       </c>
       <c r="E20" s="15">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F20" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G20" s="14">
         <v>17</v>
       </c>
       <c r="H20" s="15">
-        <v>-64.705882352941</v>
+        <v>-70.588235294117</v>
       </c>
       <c r="I20" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J20" s="14">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K20" s="15">
-        <v>-21.739130434782</v>
+        <v>-26.923076923076</v>
       </c>
       <c r="L20" s="15">
-        <v>-43.75</v>
+        <v>-45.714285714285</v>
       </c>
       <c r="M20" s="15">
-        <v>-10</v>
+        <v>-5</v>
       </c>
       <c r="N20" s="15">
-        <v>-89.285714285714</v>
+        <v>-90.256410256410</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D21" s="17">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E21" s="18">
-        <v>27.586206896551</v>
+        <v>34.615384615384</v>
       </c>
       <c r="F21" s="17">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="G21" s="17">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H21" s="18">
-        <v>4.098360655737</v>
+        <v>8.264462809917</v>
       </c>
       <c r="I21" s="17">
-        <v>295</v>
+        <v>326</v>
       </c>
       <c r="J21" s="17">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="K21" s="18">
-        <v>31.111111111111</v>
+        <v>29.880478087649</v>
       </c>
       <c r="L21" s="18">
-        <v>-4.530744336569</v>
+        <v>-4.956268221574</v>
       </c>
       <c r="M21" s="18">
-        <v>31.111111111111</v>
+        <v>31.451612903225</v>
       </c>
       <c r="N21" s="18">
-        <v>-64.628297362110</v>
+        <v>-65.319148936170</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,37 +1180,37 @@
         <v>29</v>
       </c>
       <c r="C22" s="14">
+        <v>1</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="14">
+        <v>3</v>
+      </c>
+      <c r="G22" s="14">
         <v>2</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F22" s="14">
-        <v>4</v>
-      </c>
-      <c r="G22" s="14">
-        <v>3</v>
-      </c>
       <c r="H22" s="15">
-        <v>33.333333333333</v>
+        <v>50</v>
       </c>
       <c r="I22" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J22" s="14">
         <v>3</v>
       </c>
       <c r="K22" s="15">
-        <v>66.666666666666</v>
+        <v>100</v>
       </c>
       <c r="L22" s="15">
-        <v>-37.5</v>
+        <v>-25</v>
       </c>
       <c r="M22" s="15">
-        <v>-16.666666666666</v>
+        <v>0</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1230,25 +1230,25 @@
         <v>100</v>
       </c>
       <c r="F23" s="14">
+        <v>4</v>
+      </c>
+      <c r="G23" s="14">
         <v>3</v>
       </c>
-      <c r="G23" s="14">
-        <v>2</v>
-      </c>
       <c r="H23" s="15">
-        <v>50</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I23" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J23" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K23" s="15">
-        <v>0</v>
+        <v>14.285714285714</v>
       </c>
       <c r="L23" s="15">
-        <v>-14.285714285714</v>
+        <v>14.285714285714</v>
       </c>
       <c r="M23" s="13" t="s">
         <v>21</v>
@@ -1265,34 +1265,34 @@
         <v>17</v>
       </c>
       <c r="D24" s="14">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E24" s="15">
-        <v>0</v>
+        <v>30.769230769230</v>
       </c>
       <c r="F24" s="14">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="G24" s="14">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H24" s="15">
-        <v>-12.987012987013</v>
+        <v>-1.369863013698</v>
       </c>
       <c r="I24" s="14">
-        <v>167</v>
+        <v>186</v>
       </c>
       <c r="J24" s="14">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="K24" s="15">
-        <v>-1.764705882352</v>
+        <v>1.639344262295</v>
       </c>
       <c r="L24" s="15">
-        <v>0.602409638554</v>
+        <v>3.333333333333</v>
       </c>
       <c r="M24" s="15">
-        <v>62.135922330097</v>
+        <v>56.302521008403</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D25" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E25" s="15">
-        <v>66.666666666666</v>
+        <v>0</v>
       </c>
       <c r="F25" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G25" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H25" s="15">
-        <v>-36.842105263157</v>
+        <v>-30</v>
       </c>
       <c r="I25" s="14">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J25" s="14">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="K25" s="15">
-        <v>-20.512820512820</v>
+        <v>-16.279069767441</v>
       </c>
       <c r="L25" s="15">
-        <v>-8.823529411764</v>
+        <v>-10</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D26" s="14">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E26" s="15">
         <v>-50</v>
       </c>
       <c r="F26" s="14">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G26" s="14">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="H26" s="15">
-        <v>4.255319148936</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="I26" s="14">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="J26" s="14">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="K26" s="15">
-        <v>-4.716981132075</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="L26" s="15">
-        <v>3.061224489795</v>
+        <v>-1.754385964912</v>
       </c>
       <c r="M26" s="15">
-        <v>-9.009009009009</v>
+        <v>-18.248175182481</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,7 +1385,7 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1394,13 +1394,13 @@
         <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G27" s="14">
         <v>3</v>
       </c>
       <c r="H27" s="15">
-        <v>33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="I27" s="14">
         <v>10</v>
@@ -1412,7 +1412,7 @@
         <v>100</v>
       </c>
       <c r="L27" s="15">
-        <v>42.857142857142</v>
+        <v>11.111111111111</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,7 +1426,7 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>20</v>
@@ -1435,25 +1435,25 @@
         <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G28" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H28" s="15">
-        <v>66.666666666666</v>
+        <v>300</v>
       </c>
       <c r="I28" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J28" s="14">
         <v>9</v>
       </c>
       <c r="K28" s="15">
+        <v>33.333333333333</v>
+      </c>
+      <c r="L28" s="15">
         <v>0</v>
-      </c>
-      <c r="L28" s="15">
-        <v>-10</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,11 +1469,11 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="14">
-        <v>1</v>
-      </c>
-      <c r="E29" s="15">
-        <v>-100</v>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F29" s="13" t="s">
         <v>20</v>
@@ -1497,10 +1497,10 @@
         <v>21</v>
       </c>
       <c r="M29" s="15">
-        <v>-66.666666666666</v>
+        <v>-80</v>
       </c>
       <c r="N29" s="15">
-        <v>-97.560975609756</v>
+        <v>-97.727272727272</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1510,11 +1510,11 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="14">
-        <v>1</v>
-      </c>
-      <c r="E30" s="15">
-        <v>-100</v>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F30" s="13" t="s">
         <v>20</v>
@@ -1538,10 +1538,10 @@
         <v>21</v>
       </c>
       <c r="M30" s="15">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="N30" s="15">
-        <v>-97.560975609756</v>
+        <v>-97.727272727272</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1557,8 +1557,8 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="13" t="s">
-        <v>20</v>
+      <c r="F31" s="14">
+        <v>1</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
@@ -1567,7 +1567,7 @@
         <v>21</v>
       </c>
       <c r="I31" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J31" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-083pct.xlsx
+++ b/data/source/weekly/cs-en-us-083pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">11</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/2/2026</t>
+      <t xml:space="preserve">3/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/8/2026</t>
+      <t xml:space="preserve">3/15/2026</t>
     </r>
   </si>
   <si>
@@ -854,17 +854,17 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="14">
+      <c r="D14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G14" s="14">
         <v>1</v>
-      </c>
-      <c r="E14" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G14" s="14">
-        <v>2</v>
       </c>
       <c r="H14" s="15">
         <v>-100</v>
@@ -893,7 +893,7 @@
         <v>22</v>
       </c>
       <c r="C15" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -902,31 +902,31 @@
         <v>21</v>
       </c>
       <c r="F15" s="14">
+        <v>5</v>
+      </c>
+      <c r="G15" s="14">
         <v>2</v>
       </c>
-      <c r="G15" s="14">
-        <v>3</v>
-      </c>
       <c r="H15" s="15">
-        <v>-33.333333333333</v>
+        <v>150</v>
       </c>
       <c r="I15" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J15" s="14">
         <v>5</v>
       </c>
       <c r="K15" s="15">
-        <v>80</v>
+        <v>140</v>
       </c>
       <c r="L15" s="15">
         <v>50</v>
       </c>
       <c r="M15" s="15">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N15" s="15">
-        <v>-47.058823529411</v>
+        <v>-29.411764705882</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D16" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E16" s="15">
-        <v>100</v>
+        <v>133.333333333333</v>
       </c>
       <c r="F16" s="14">
         <v>26</v>
       </c>
       <c r="G16" s="14">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H16" s="15">
-        <v>85.714285714285</v>
+        <v>160</v>
       </c>
       <c r="I16" s="14">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="J16" s="14">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K16" s="15">
-        <v>124</v>
+        <v>121.428571428571</v>
       </c>
       <c r="L16" s="15">
-        <v>-17.647058823529</v>
+        <v>-21.518987341772</v>
       </c>
       <c r="M16" s="15">
-        <v>-18.840579710144</v>
+        <v>-22.5</v>
       </c>
       <c r="N16" s="15">
-        <v>-77.327935222672</v>
+        <v>-77.935943060498</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,37 +978,37 @@
         <v>9</v>
       </c>
       <c r="D17" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E17" s="15">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="F17" s="14">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G17" s="14">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H17" s="15">
-        <v>29.166666666666</v>
+        <v>26.923076923076</v>
       </c>
       <c r="I17" s="14">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="J17" s="14">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="K17" s="15">
-        <v>16.129032258064</v>
+        <v>22.388059701492</v>
       </c>
       <c r="L17" s="15">
-        <v>1.408450704225</v>
+        <v>1.234567901234</v>
       </c>
       <c r="M17" s="15">
-        <v>75.609756097561</v>
+        <v>86.363636363636</v>
       </c>
       <c r="N17" s="15">
-        <v>-50</v>
+        <v>-46.405228758169</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D18" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18" s="15">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="F18" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G18" s="14">
         <v>12</v>
       </c>
       <c r="H18" s="15">
-        <v>50</v>
+        <v>58.333333333333</v>
       </c>
       <c r="I18" s="14">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="J18" s="14">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K18" s="15">
-        <v>55.172413793103</v>
+        <v>63.333333333333</v>
       </c>
       <c r="L18" s="15">
-        <v>-18.181818181818</v>
+        <v>-12.5</v>
       </c>
       <c r="M18" s="15">
-        <v>-22.413793103448</v>
+        <v>-25.757575757575</v>
       </c>
       <c r="N18" s="15">
-        <v>-81.481481481481</v>
+        <v>-81.297709923664</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D19" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E19" s="15">
-        <v>10</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="F19" s="14">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G19" s="14">
         <v>49</v>
       </c>
       <c r="H19" s="15">
-        <v>0</v>
+        <v>-2.040816326530</v>
       </c>
       <c r="I19" s="14">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="J19" s="14">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="K19" s="15">
-        <v>23.762376237623</v>
+        <v>18.421052631578</v>
       </c>
       <c r="L19" s="15">
-        <v>15.740740740740</v>
+        <v>15.384615384615</v>
       </c>
       <c r="M19" s="15">
-        <v>135.849056603774</v>
+        <v>110.9375</v>
       </c>
       <c r="N19" s="15">
-        <v>48.809523809523</v>
+        <v>48.351648351648</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,37 +1101,37 @@
         <v>1</v>
       </c>
       <c r="D20" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E20" s="15">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="F20" s="14">
         <v>5</v>
       </c>
       <c r="G20" s="14">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H20" s="15">
-        <v>-70.588235294117</v>
+        <v>-58.333333333333</v>
       </c>
       <c r="I20" s="14">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J20" s="14">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K20" s="15">
-        <v>-26.923076923076</v>
+        <v>-25</v>
       </c>
       <c r="L20" s="15">
-        <v>-45.714285714285</v>
+        <v>-50</v>
       </c>
       <c r="M20" s="15">
-        <v>-5</v>
+        <v>-12.5</v>
       </c>
       <c r="N20" s="15">
-        <v>-90.256410256410</v>
+        <v>-89.952153110047</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D21" s="17">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E21" s="18">
-        <v>34.615384615384</v>
+        <v>50</v>
       </c>
       <c r="F21" s="17">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="G21" s="17">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="H21" s="18">
-        <v>8.264462809917</v>
+        <v>21.428571428571</v>
       </c>
       <c r="I21" s="17">
-        <v>326</v>
+        <v>361</v>
       </c>
       <c r="J21" s="17">
-        <v>251</v>
+        <v>275</v>
       </c>
       <c r="K21" s="18">
-        <v>29.880478087649</v>
+        <v>31.272727272727</v>
       </c>
       <c r="L21" s="18">
-        <v>-4.956268221574</v>
+        <v>-5.744125326370</v>
       </c>
       <c r="M21" s="18">
-        <v>31.451612903225</v>
+        <v>26.666666666666</v>
       </c>
       <c r="N21" s="18">
-        <v>-65.319148936170</v>
+        <v>-64.711632453567</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1189,28 +1189,28 @@
         <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>3</v>
-      </c>
-      <c r="G22" s="14">
-        <v>2</v>
-      </c>
-      <c r="H22" s="15">
-        <v>50</v>
+        <v>4</v>
+      </c>
+      <c r="G22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I22" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J22" s="14">
         <v>3</v>
       </c>
       <c r="K22" s="15">
-        <v>100</v>
+        <v>133.333333333333</v>
       </c>
       <c r="L22" s="15">
-        <v>-25</v>
+        <v>-12.5</v>
       </c>
       <c r="M22" s="15">
-        <v>0</v>
+        <v>16.666666666666</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
+        <v>1</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F23" s="14">
+        <v>5</v>
+      </c>
+      <c r="G23" s="14">
         <v>2</v>
       </c>
-      <c r="D23" s="14">
-        <v>1</v>
-      </c>
-      <c r="E23" s="15">
-        <v>100</v>
-      </c>
-      <c r="F23" s="14">
-        <v>4</v>
-      </c>
-      <c r="G23" s="14">
-        <v>3</v>
-      </c>
       <c r="H23" s="15">
-        <v>33.333333333333</v>
+        <v>150</v>
       </c>
       <c r="I23" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J23" s="14">
         <v>7</v>
       </c>
       <c r="K23" s="15">
-        <v>14.285714285714</v>
+        <v>28.571428571428</v>
       </c>
       <c r="L23" s="15">
-        <v>14.285714285714</v>
-      </c>
-      <c r="M23" s="13" t="s">
-        <v>21</v>
+        <v>12.5</v>
+      </c>
+      <c r="M23" s="15">
+        <v>800</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D24" s="14">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E24" s="15">
-        <v>30.769230769230</v>
+        <v>111.111111111111</v>
       </c>
       <c r="F24" s="14">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="G24" s="14">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="H24" s="15">
-        <v>-1.369863013698</v>
+        <v>45.283018867924</v>
       </c>
       <c r="I24" s="14">
-        <v>186</v>
+        <v>204</v>
       </c>
       <c r="J24" s="14">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="K24" s="15">
-        <v>1.639344262295</v>
+        <v>6.25</v>
       </c>
       <c r="L24" s="15">
-        <v>3.333333333333</v>
+        <v>4.081632653061</v>
       </c>
       <c r="M24" s="15">
-        <v>56.302521008403</v>
+        <v>51.111111111111</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D25" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E25" s="15">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="F25" s="14">
+        <v>18</v>
+      </c>
+      <c r="G25" s="14">
         <v>14</v>
       </c>
-      <c r="G25" s="14">
-        <v>20</v>
-      </c>
       <c r="H25" s="15">
-        <v>-30</v>
+        <v>28.571428571428</v>
       </c>
       <c r="I25" s="14">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="J25" s="14">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K25" s="15">
-        <v>-16.279069767441</v>
+        <v>-6.666666666666</v>
       </c>
       <c r="L25" s="15">
-        <v>-10</v>
+        <v>-10.638297872340</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D26" s="14">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E26" s="15">
-        <v>-50</v>
+        <v>8.333333333333</v>
       </c>
       <c r="F26" s="14">
         <v>45</v>
       </c>
       <c r="G26" s="14">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H26" s="15">
-        <v>-18.181818181818</v>
+        <v>-22.413793103448</v>
       </c>
       <c r="I26" s="14">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="J26" s="14">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="K26" s="15">
-        <v>-11.111111111111</v>
+        <v>-10.144927536231</v>
       </c>
       <c r="L26" s="15">
-        <v>-1.754385964912</v>
+        <v>-8.823529411764</v>
       </c>
       <c r="M26" s="15">
-        <v>-18.248175182481</v>
+        <v>-16.778523489932</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,7 +1385,7 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1394,25 +1394,25 @@
         <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G27" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H27" s="15">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I27" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J27" s="14">
         <v>5</v>
       </c>
       <c r="K27" s="15">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="L27" s="15">
-        <v>11.111111111111</v>
+        <v>8.333333333333</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>3</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="D28" s="14">
+        <v>1</v>
+      </c>
+      <c r="E28" s="15">
+        <v>0</v>
       </c>
       <c r="F28" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G28" s="14">
         <v>2</v>
       </c>
       <c r="H28" s="15">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="I28" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J28" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K28" s="15">
-        <v>33.333333333333</v>
+        <v>30</v>
       </c>
       <c r="L28" s="15">
-        <v>0</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,11 +1469,11 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="D29" s="14">
+        <v>1</v>
+      </c>
+      <c r="E29" s="15">
+        <v>-100</v>
       </c>
       <c r="F29" s="13" t="s">
         <v>20</v>
@@ -1488,10 +1488,10 @@
         <v>1</v>
       </c>
       <c r="J29" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K29" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L29" s="13" t="s">
         <v>21</v>
@@ -1500,7 +1500,7 @@
         <v>-80</v>
       </c>
       <c r="N29" s="15">
-        <v>-97.727272727272</v>
+        <v>-97.826086956521</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1510,11 +1510,11 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="D30" s="14">
+        <v>1</v>
+      </c>
+      <c r="E30" s="15">
+        <v>-100</v>
       </c>
       <c r="F30" s="13" t="s">
         <v>20</v>
@@ -1529,10 +1529,10 @@
         <v>1</v>
       </c>
       <c r="J30" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K30" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L30" s="13" t="s">
         <v>21</v>
@@ -1541,7 +1541,7 @@
         <v>-75</v>
       </c>
       <c r="N30" s="15">
-        <v>-97.727272727272</v>
+        <v>-97.826086956521</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-083pct.xlsx
+++ b/data/source/weekly/cs-en-us-083pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">12</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/9/2026</t>
+      <t xml:space="preserve">3/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/15/2026</t>
+      <t xml:space="preserve">3/22/2026</t>
     </r>
   </si>
   <si>
@@ -893,7 +893,7 @@
         <v>22</v>
       </c>
       <c r="C15" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -902,31 +902,31 @@
         <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>5</v>
-      </c>
-      <c r="G15" s="14">
-        <v>2</v>
-      </c>
-      <c r="H15" s="15">
-        <v>150</v>
+        <v>7</v>
+      </c>
+      <c r="G15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I15" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J15" s="14">
         <v>5</v>
       </c>
       <c r="K15" s="15">
-        <v>140</v>
+        <v>180</v>
       </c>
       <c r="L15" s="15">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="M15" s="15">
-        <v>100</v>
+        <v>133.333333333333</v>
       </c>
       <c r="N15" s="15">
-        <v>-29.411764705882</v>
+        <v>-26.315789473684</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D16" s="14">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E16" s="15">
-        <v>133.333333333333</v>
+        <v>-69.230769230769</v>
       </c>
       <c r="F16" s="14">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G16" s="14">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="H16" s="15">
-        <v>160</v>
+        <v>28.571428571428</v>
       </c>
       <c r="I16" s="14">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="J16" s="14">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="K16" s="15">
-        <v>121.428571428571</v>
+        <v>60.975609756097</v>
       </c>
       <c r="L16" s="15">
-        <v>-21.518987341772</v>
+        <v>-25.842696629213</v>
       </c>
       <c r="M16" s="15">
-        <v>-22.5</v>
+        <v>-27.472527472527</v>
       </c>
       <c r="N16" s="15">
-        <v>-77.935943060498</v>
+        <v>-78.913738019169</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -984,31 +984,31 @@
         <v>80</v>
       </c>
       <c r="F17" s="14">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G17" s="14">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H17" s="15">
-        <v>26.923076923076</v>
+        <v>54.166666666666</v>
       </c>
       <c r="I17" s="14">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J17" s="14">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="K17" s="15">
-        <v>22.388059701492</v>
+        <v>30.555555555555</v>
       </c>
       <c r="L17" s="15">
-        <v>1.234567901234</v>
+        <v>5.617977528089</v>
       </c>
       <c r="M17" s="15">
-        <v>86.363636363636</v>
+        <v>88</v>
       </c>
       <c r="N17" s="15">
-        <v>-46.405228758169</v>
+        <v>-44.705882352941</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
+        <v>3</v>
+      </c>
+      <c r="D18" s="14">
         <v>4</v>
       </c>
-      <c r="D18" s="14">
-        <v>1</v>
-      </c>
       <c r="E18" s="15">
-        <v>300</v>
+        <v>-25</v>
       </c>
       <c r="F18" s="14">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G18" s="14">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H18" s="15">
-        <v>58.333333333333</v>
+        <v>50</v>
       </c>
       <c r="I18" s="14">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J18" s="14">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="K18" s="15">
-        <v>63.333333333333</v>
+        <v>47.058823529411</v>
       </c>
       <c r="L18" s="15">
-        <v>-12.5</v>
+        <v>-12.280701754386</v>
       </c>
       <c r="M18" s="15">
-        <v>-25.757575757575</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="N18" s="15">
-        <v>-81.297709923664</v>
+        <v>-82.578397212543</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D19" s="14">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E19" s="15">
-        <v>-7.692307692307</v>
+        <v>128.571428571429</v>
       </c>
       <c r="F19" s="14">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="G19" s="14">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="H19" s="15">
-        <v>-2.040816326530</v>
+        <v>18.181818181818</v>
       </c>
       <c r="I19" s="14">
-        <v>135</v>
+        <v>154</v>
       </c>
       <c r="J19" s="14">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="K19" s="15">
-        <v>18.421052631578</v>
+        <v>27.272727272727</v>
       </c>
       <c r="L19" s="15">
-        <v>15.384615384615</v>
+        <v>20.3125</v>
       </c>
       <c r="M19" s="15">
-        <v>110.9375</v>
+        <v>129.850746268657</v>
       </c>
       <c r="N19" s="15">
-        <v>48.351648351648</v>
+        <v>45.283018867924</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,37 +1101,37 @@
         <v>1</v>
       </c>
       <c r="D20" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E20" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F20" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G20" s="14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H20" s="15">
-        <v>-58.333333333333</v>
+        <v>-63.636363636363</v>
       </c>
       <c r="I20" s="14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J20" s="14">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K20" s="15">
-        <v>-25</v>
+        <v>-29.032258064516</v>
       </c>
       <c r="L20" s="15">
-        <v>-50</v>
+        <v>-48.837209302325</v>
       </c>
       <c r="M20" s="15">
-        <v>-12.5</v>
+        <v>-24.137931034482</v>
       </c>
       <c r="N20" s="15">
-        <v>-89.952153110047</v>
+        <v>-90.557939914163</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D21" s="17">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="E21" s="18">
-        <v>50</v>
+        <v>9.375</v>
       </c>
       <c r="F21" s="17">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="G21" s="17">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H21" s="18">
-        <v>21.428571428571</v>
+        <v>27.927927927927</v>
       </c>
       <c r="I21" s="17">
-        <v>361</v>
+        <v>400</v>
       </c>
       <c r="J21" s="17">
-        <v>275</v>
+        <v>307</v>
       </c>
       <c r="K21" s="18">
-        <v>31.272727272727</v>
+        <v>30.293159609120</v>
       </c>
       <c r="L21" s="18">
-        <v>-5.744125326370</v>
+        <v>-3.381642512077</v>
       </c>
       <c r="M21" s="18">
-        <v>26.666666666666</v>
+        <v>27.388535031847</v>
       </c>
       <c r="N21" s="18">
-        <v>-64.711632453567</v>
+        <v>-64.881474978050</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>1</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1210,7 +1210,7 @@
         <v>-12.5</v>
       </c>
       <c r="M22" s="15">
-        <v>16.666666666666</v>
+        <v>0</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>1</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
+        <v>2</v>
+      </c>
+      <c r="D23" s="14">
+        <v>2</v>
+      </c>
+      <c r="E23" s="15">
+        <v>0</v>
       </c>
       <c r="F23" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G23" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H23" s="15">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="I23" s="14">
+        <v>12</v>
+      </c>
+      <c r="J23" s="14">
         <v>9</v>
       </c>
-      <c r="J23" s="14">
-        <v>7</v>
-      </c>
       <c r="K23" s="15">
-        <v>28.571428571428</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L23" s="15">
-        <v>12.5</v>
+        <v>50</v>
       </c>
       <c r="M23" s="15">
-        <v>800</v>
+        <v>1100</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D24" s="14">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E24" s="15">
-        <v>111.111111111111</v>
+        <v>100</v>
       </c>
       <c r="F24" s="14">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="G24" s="14">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H24" s="15">
-        <v>45.283018867924</v>
+        <v>57.692307692307</v>
       </c>
       <c r="I24" s="14">
-        <v>204</v>
+        <v>230</v>
       </c>
       <c r="J24" s="14">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="K24" s="15">
-        <v>6.25</v>
+        <v>12.195121951219</v>
       </c>
       <c r="L24" s="15">
-        <v>4.081632653061</v>
+        <v>4.072398190045</v>
       </c>
       <c r="M24" s="15">
-        <v>51.111111111111</v>
+        <v>52.317880794702</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
+        <v>6</v>
+      </c>
+      <c r="D25" s="14">
         <v>5</v>
       </c>
-      <c r="D25" s="14">
-        <v>2</v>
-      </c>
       <c r="E25" s="15">
-        <v>150</v>
+        <v>20</v>
       </c>
       <c r="F25" s="14">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G25" s="14">
         <v>14</v>
       </c>
       <c r="H25" s="15">
-        <v>28.571428571428</v>
+        <v>42.857142857142</v>
       </c>
       <c r="I25" s="14">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="J25" s="14">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="K25" s="15">
-        <v>-6.666666666666</v>
+        <v>-6</v>
       </c>
       <c r="L25" s="15">
-        <v>-10.638297872340</v>
+        <v>-12.962962962963</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D26" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E26" s="15">
-        <v>8.333333333333</v>
+        <v>42.857142857142</v>
       </c>
       <c r="F26" s="14">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="G26" s="14">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="H26" s="15">
-        <v>-22.413793103448</v>
+        <v>-17.1875</v>
       </c>
       <c r="I26" s="14">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="J26" s="14">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="K26" s="15">
-        <v>-10.144927536231</v>
+        <v>-4.605263157894</v>
       </c>
       <c r="L26" s="15">
-        <v>-8.823529411764</v>
+        <v>-2.684563758389</v>
       </c>
       <c r="M26" s="15">
-        <v>-16.778523489932</v>
+        <v>-10.493827160493</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,7 +1385,7 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1394,25 +1394,25 @@
         <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>6</v>
-      </c>
-      <c r="G27" s="14">
-        <v>2</v>
-      </c>
-      <c r="H27" s="15">
-        <v>200</v>
+        <v>8</v>
+      </c>
+      <c r="G27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I27" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J27" s="14">
         <v>5</v>
       </c>
       <c r="K27" s="15">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="L27" s="15">
-        <v>8.333333333333</v>
+        <v>15.384615384615</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>1</v>
-      </c>
-      <c r="D28" s="14">
-        <v>1</v>
-      </c>
-      <c r="E28" s="15">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
         <v>7</v>
       </c>
       <c r="G28" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H28" s="15">
-        <v>250</v>
+        <v>600</v>
       </c>
       <c r="I28" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J28" s="14">
         <v>10</v>
       </c>
       <c r="K28" s="15">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="L28" s="15">
-        <v>-7.142857142857</v>
+        <v>-6.25</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1470,7 +1470,7 @@
         <v>20</v>
       </c>
       <c r="D29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E29" s="15">
         <v>-100</v>
@@ -1479,7 +1479,7 @@
         <v>20</v>
       </c>
       <c r="G29" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H29" s="15">
         <v>-100</v>
@@ -1488,19 +1488,19 @@
         <v>1</v>
       </c>
       <c r="J29" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K29" s="15">
-        <v>-66.666666666666</v>
+        <v>-80</v>
       </c>
       <c r="L29" s="13" t="s">
         <v>21</v>
       </c>
       <c r="M29" s="15">
-        <v>-80</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="N29" s="15">
-        <v>-97.826086956521</v>
+        <v>-98.039215686274</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1520,7 +1520,7 @@
         <v>20</v>
       </c>
       <c r="G30" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H30" s="15">
         <v>-100</v>
@@ -1529,19 +1529,19 @@
         <v>1</v>
       </c>
       <c r="J30" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K30" s="15">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="L30" s="13" t="s">
         <v>21</v>
       </c>
       <c r="M30" s="15">
-        <v>-75</v>
+        <v>-80</v>
       </c>
       <c r="N30" s="15">
-        <v>-97.826086956521</v>
+        <v>-98.039215686274</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1557,8 +1557,8 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="14">
-        <v>1</v>
+      <c r="F31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-083pct.xlsx
+++ b/data/source/weekly/cs-en-us-083pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve">13</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/16/2026</t>
+      <t xml:space="preserve">3/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/22/2026</t>
+      <t xml:space="preserve">3/29/2026</t>
     </r>
   </si>
   <si>
@@ -893,7 +893,7 @@
         <v>22</v>
       </c>
       <c r="C15" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -902,7 +902,7 @@
         <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>20</v>
@@ -920,13 +920,13 @@
         <v>180</v>
       </c>
       <c r="L15" s="15">
-        <v>75</v>
+        <v>55.555555555555</v>
       </c>
       <c r="M15" s="15">
-        <v>133.333333333333</v>
+        <v>100</v>
       </c>
       <c r="N15" s="15">
-        <v>-26.315789473684</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,37 +937,37 @@
         <v>4</v>
       </c>
       <c r="D16" s="14">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="E16" s="15">
-        <v>-69.230769230769</v>
+        <v>100</v>
       </c>
       <c r="F16" s="14">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="G16" s="14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H16" s="15">
-        <v>28.571428571428</v>
+        <v>4.545454545454</v>
       </c>
       <c r="I16" s="14">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="J16" s="14">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="K16" s="15">
-        <v>60.975609756097</v>
+        <v>62.790697674418</v>
       </c>
       <c r="L16" s="15">
-        <v>-25.842696629213</v>
+        <v>-24.731182795698</v>
       </c>
       <c r="M16" s="15">
-        <v>-27.472527472527</v>
+        <v>-27.835051546391</v>
       </c>
       <c r="N16" s="15">
-        <v>-78.913738019169</v>
+        <v>-79.472140762463</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D17" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E17" s="15">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="F17" s="14">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G17" s="14">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H17" s="15">
-        <v>54.166666666666</v>
+        <v>56.521739130434</v>
       </c>
       <c r="I17" s="14">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="J17" s="14">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="K17" s="15">
-        <v>30.555555555555</v>
+        <v>27.848101265822</v>
       </c>
       <c r="L17" s="15">
-        <v>5.617977528089</v>
+        <v>2.020202020202</v>
       </c>
       <c r="M17" s="15">
-        <v>88</v>
+        <v>87.037037037037</v>
       </c>
       <c r="N17" s="15">
-        <v>-44.705882352941</v>
+        <v>-46.276595744680</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D18" s="14">
         <v>4</v>
       </c>
       <c r="E18" s="15">
-        <v>-25</v>
+        <v>50</v>
       </c>
       <c r="F18" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G18" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H18" s="15">
-        <v>50</v>
+        <v>54.545454545454</v>
       </c>
       <c r="I18" s="14">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="J18" s="14">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K18" s="15">
-        <v>47.058823529411</v>
+        <v>47.368421052631</v>
       </c>
       <c r="L18" s="15">
-        <v>-12.280701754386</v>
+        <v>-3.448275862068</v>
       </c>
       <c r="M18" s="15">
-        <v>-28.571428571428</v>
+        <v>-23.287671232876</v>
       </c>
       <c r="N18" s="15">
-        <v>-82.578397212543</v>
+        <v>-82.389937106918</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D19" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E19" s="15">
-        <v>128.571428571429</v>
+        <v>200</v>
       </c>
       <c r="F19" s="14">
         <v>52</v>
       </c>
       <c r="G19" s="14">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="H19" s="15">
-        <v>18.181818181818</v>
+        <v>52.941176470588</v>
       </c>
       <c r="I19" s="14">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="J19" s="14">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="K19" s="15">
-        <v>27.272727272727</v>
+        <v>32</v>
       </c>
       <c r="L19" s="15">
-        <v>20.3125</v>
+        <v>16.197183098591</v>
       </c>
       <c r="M19" s="15">
-        <v>129.850746268657</v>
+        <v>122.972972972973</v>
       </c>
       <c r="N19" s="15">
-        <v>45.283018867924</v>
+        <v>36.363636363636</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1107,31 +1107,31 @@
         <v>-66.666666666666</v>
       </c>
       <c r="F20" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G20" s="14">
         <v>11</v>
       </c>
       <c r="H20" s="15">
-        <v>-63.636363636363</v>
+        <v>-54.545454545454</v>
       </c>
       <c r="I20" s="14">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J20" s="14">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K20" s="15">
-        <v>-29.032258064516</v>
+        <v>-32.352941176470</v>
       </c>
       <c r="L20" s="15">
-        <v>-48.837209302325</v>
+        <v>-52.083333333333</v>
       </c>
       <c r="M20" s="15">
-        <v>-24.137931034482</v>
+        <v>-25.806451612903</v>
       </c>
       <c r="N20" s="15">
-        <v>-90.557939914163</v>
+        <v>-90.944881889763</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D21" s="17">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="E21" s="18">
-        <v>9.375</v>
+        <v>55</v>
       </c>
       <c r="F21" s="17">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="G21" s="17">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="H21" s="18">
-        <v>27.927927927927</v>
+        <v>36.274509803921</v>
       </c>
       <c r="I21" s="17">
-        <v>400</v>
+        <v>429</v>
       </c>
       <c r="J21" s="17">
-        <v>307</v>
+        <v>327</v>
       </c>
       <c r="K21" s="18">
-        <v>30.293159609120</v>
+        <v>31.192660550458</v>
       </c>
       <c r="L21" s="18">
-        <v>-3.381642512077</v>
+        <v>-4.454342984409</v>
       </c>
       <c r="M21" s="18">
-        <v>27.388535031847</v>
+        <v>27.299703264095</v>
       </c>
       <c r="N21" s="18">
-        <v>-64.881474978050</v>
+        <v>-65.789473684210</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1189,7 +1189,7 @@
         <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>20</v>
@@ -1207,7 +1207,7 @@
         <v>133.333333333333</v>
       </c>
       <c r="L22" s="15">
-        <v>-12.5</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="M22" s="15">
         <v>0</v>
@@ -1220,32 +1220,32 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="14">
-        <v>2</v>
+      <c r="C23" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D23" s="14">
         <v>2</v>
       </c>
       <c r="E23" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F23" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G23" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H23" s="15">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="I23" s="14">
         <v>12</v>
       </c>
       <c r="J23" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K23" s="15">
-        <v>33.333333333333</v>
+        <v>9.090909090909</v>
       </c>
       <c r="L23" s="15">
         <v>50</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D24" s="14">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="E24" s="15">
-        <v>100</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="F24" s="14">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G24" s="14">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="H24" s="15">
-        <v>57.692307692307</v>
+        <v>42.105263157894</v>
       </c>
       <c r="I24" s="14">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="J24" s="14">
-        <v>205</v>
+        <v>227</v>
       </c>
       <c r="K24" s="15">
-        <v>12.195121951219</v>
+        <v>9.251101321585</v>
       </c>
       <c r="L24" s="15">
-        <v>4.072398190045</v>
+        <v>5.531914893617</v>
       </c>
       <c r="M24" s="15">
-        <v>52.317880794702</v>
+        <v>54.037267080745</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
+        <v>5</v>
+      </c>
+      <c r="D25" s="14">
         <v>6</v>
       </c>
-      <c r="D25" s="14">
-        <v>5</v>
-      </c>
       <c r="E25" s="15">
-        <v>20</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F25" s="14">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G25" s="14">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H25" s="15">
-        <v>42.857142857142</v>
+        <v>11.764705882352</v>
       </c>
       <c r="I25" s="14">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="J25" s="14">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="K25" s="15">
-        <v>-6</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="L25" s="15">
-        <v>-12.962962962963</v>
+        <v>-8.771929824561</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="D26" s="14">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E26" s="15">
-        <v>42.857142857142</v>
+        <v>-30</v>
       </c>
       <c r="F26" s="14">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G26" s="14">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="H26" s="15">
-        <v>-17.1875</v>
+        <v>-8.928571428571</v>
       </c>
       <c r="I26" s="14">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="J26" s="14">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="K26" s="15">
-        <v>-4.605263157894</v>
+        <v>-6.172839506172</v>
       </c>
       <c r="L26" s="15">
-        <v>-2.684563758389</v>
+        <v>-4.402515723270</v>
       </c>
       <c r="M26" s="15">
-        <v>-10.493827160493</v>
+        <v>-14.124293785310</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,7 +1385,7 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1394,7 +1394,7 @@
         <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G27" s="13" t="s">
         <v>20</v>
@@ -1412,7 +1412,7 @@
         <v>200</v>
       </c>
       <c r="L27" s="15">
-        <v>15.384615384615</v>
+        <v>7.142857142857</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,32 +1425,32 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="14">
+        <v>1</v>
+      </c>
+      <c r="E28" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F28" s="14">
+        <v>6</v>
+      </c>
+      <c r="G28" s="14">
         <v>2</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F28" s="14">
-        <v>7</v>
-      </c>
-      <c r="G28" s="14">
-        <v>1</v>
-      </c>
       <c r="H28" s="15">
-        <v>600</v>
+        <v>200</v>
       </c>
       <c r="I28" s="14">
         <v>15</v>
       </c>
       <c r="J28" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K28" s="15">
-        <v>50</v>
+        <v>36.363636363636</v>
       </c>
       <c r="L28" s="15">
         <v>-6.25</v>
@@ -1470,7 +1470,7 @@
         <v>20</v>
       </c>
       <c r="D29" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E29" s="15">
         <v>-100</v>
@@ -1488,19 +1488,19 @@
         <v>1</v>
       </c>
       <c r="J29" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K29" s="15">
-        <v>-80</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="L29" s="13" t="s">
         <v>21</v>
       </c>
       <c r="M29" s="15">
-        <v>-83.333333333333</v>
+        <v>-85.714285714285</v>
       </c>
       <c r="N29" s="15">
-        <v>-98.039215686274</v>
+        <v>-98.113207547169</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1529,19 +1529,19 @@
         <v>1</v>
       </c>
       <c r="J30" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K30" s="15">
-        <v>-75</v>
+        <v>-80</v>
       </c>
       <c r="L30" s="13" t="s">
         <v>21</v>
       </c>
       <c r="M30" s="15">
-        <v>-80</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="N30" s="15">
-        <v>-98.039215686274</v>
+        <v>-98.113207547169</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-083pct.xlsx
+++ b/data/source/weekly/cs-en-us-083pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">14</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/23/2026</t>
+      <t xml:space="preserve">3/30/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/29/2026</t>
+      <t xml:space="preserve">4/5/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -863,11 +863,11 @@
       <c r="F14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="14">
-        <v>1</v>
-      </c>
-      <c r="H14" s="15">
-        <v>-100</v>
+      <c r="G14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I14" s="13" t="s">
         <v>20</v>
@@ -911,22 +911,22 @@
         <v>21</v>
       </c>
       <c r="I15" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J15" s="14">
         <v>5</v>
       </c>
       <c r="K15" s="15">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="L15" s="15">
-        <v>55.555555555555</v>
+        <v>66.666666666666</v>
       </c>
       <c r="M15" s="15">
-        <v>100</v>
+        <v>114.285714285714</v>
       </c>
       <c r="N15" s="15">
-        <v>-30</v>
+        <v>-31.818181818181</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,37 +937,37 @@
         <v>4</v>
       </c>
       <c r="D16" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E16" s="15">
-        <v>100</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F16" s="14">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G16" s="14">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H16" s="15">
-        <v>4.545454545454</v>
+        <v>-4.761904761904</v>
       </c>
       <c r="I16" s="14">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="J16" s="14">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K16" s="15">
-        <v>62.790697674418</v>
+        <v>60.869565217391</v>
       </c>
       <c r="L16" s="15">
-        <v>-24.731182795698</v>
+        <v>-26</v>
       </c>
       <c r="M16" s="15">
-        <v>-27.835051546391</v>
+        <v>-28.846153846153</v>
       </c>
       <c r="N16" s="15">
-        <v>-79.472140762463</v>
+        <v>-80.107526881720</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D17" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E17" s="15">
         <v>0</v>
       </c>
       <c r="F17" s="14">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G17" s="14">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H17" s="15">
-        <v>56.521739130434</v>
+        <v>44.444444444444</v>
       </c>
       <c r="I17" s="14">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="J17" s="14">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="K17" s="15">
-        <v>27.848101265822</v>
+        <v>26.966292134831</v>
       </c>
       <c r="L17" s="15">
-        <v>2.020202020202</v>
+        <v>2.727272727272</v>
       </c>
       <c r="M17" s="15">
-        <v>87.037037037037</v>
+        <v>76.5625</v>
       </c>
       <c r="N17" s="15">
-        <v>-46.276595744680</v>
+        <v>-47.441860465116</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D18" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E18" s="15">
-        <v>50</v>
+        <v>600</v>
       </c>
       <c r="F18" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G18" s="14">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H18" s="15">
-        <v>54.545454545454</v>
+        <v>80</v>
       </c>
       <c r="I18" s="14">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="J18" s="14">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K18" s="15">
-        <v>47.368421052631</v>
+        <v>58.974358974359</v>
       </c>
       <c r="L18" s="15">
-        <v>-3.448275862068</v>
+        <v>0</v>
       </c>
       <c r="M18" s="15">
-        <v>-23.287671232876</v>
+        <v>-17.333333333333</v>
       </c>
       <c r="N18" s="15">
-        <v>-82.389937106918</v>
+        <v>-81.764705882352</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D19" s="14">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E19" s="15">
-        <v>200</v>
+        <v>62.5</v>
       </c>
       <c r="F19" s="14">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G19" s="14">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H19" s="15">
-        <v>52.941176470588</v>
+        <v>75</v>
       </c>
       <c r="I19" s="14">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="J19" s="14">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="K19" s="15">
-        <v>32</v>
+        <v>35.338345864661</v>
       </c>
       <c r="L19" s="15">
-        <v>16.197183098591</v>
+        <v>11.111111111111</v>
       </c>
       <c r="M19" s="15">
-        <v>122.972972972973</v>
+        <v>136.842105263158</v>
       </c>
       <c r="N19" s="15">
-        <v>36.363636363636</v>
+        <v>31.386861313868</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D20" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E20" s="15">
-        <v>-66.666666666666</v>
+        <v>50</v>
       </c>
       <c r="F20" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G20" s="14">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H20" s="15">
-        <v>-54.545454545454</v>
+        <v>-40</v>
       </c>
       <c r="I20" s="14">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J20" s="14">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K20" s="15">
-        <v>-32.352941176470</v>
+        <v>-27.777777777777</v>
       </c>
       <c r="L20" s="15">
-        <v>-52.083333333333</v>
+        <v>-49.019607843137</v>
       </c>
       <c r="M20" s="15">
-        <v>-25.806451612903</v>
+        <v>-23.529411764705</v>
       </c>
       <c r="N20" s="15">
-        <v>-90.944881889763</v>
+        <v>-90.545454545454</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="D21" s="17">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E21" s="18">
-        <v>55</v>
+        <v>58.333333333333</v>
       </c>
       <c r="F21" s="17">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="G21" s="17">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H21" s="18">
-        <v>36.274509803921</v>
+        <v>45</v>
       </c>
       <c r="I21" s="17">
-        <v>429</v>
+        <v>470</v>
       </c>
       <c r="J21" s="17">
-        <v>327</v>
+        <v>351</v>
       </c>
       <c r="K21" s="18">
-        <v>31.192660550458</v>
+        <v>33.903133903133</v>
       </c>
       <c r="L21" s="18">
-        <v>-4.454342984409</v>
+        <v>-4.858299595141</v>
       </c>
       <c r="M21" s="18">
-        <v>27.299703264095</v>
+        <v>29.834254143646</v>
       </c>
       <c r="N21" s="18">
-        <v>-65.789473684210</v>
+        <v>-65.768390386016</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1189,7 +1189,7 @@
         <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>20</v>
@@ -1207,7 +1207,7 @@
         <v>133.333333333333</v>
       </c>
       <c r="L22" s="15">
-        <v>-36.363636363636</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="M22" s="15">
         <v>0</v>
@@ -1223,35 +1223,35 @@
       <c r="C23" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D23" s="14">
-        <v>2</v>
-      </c>
-      <c r="E23" s="15">
-        <v>-100</v>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F23" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G23" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H23" s="15">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I23" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J23" s="14">
         <v>11</v>
       </c>
       <c r="K23" s="15">
-        <v>9.090909090909</v>
+        <v>18.181818181818</v>
       </c>
       <c r="L23" s="15">
-        <v>50</v>
+        <v>62.5</v>
       </c>
       <c r="M23" s="15">
-        <v>1100</v>
+        <v>550</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D24" s="14">
         <v>22</v>
       </c>
       <c r="E24" s="15">
-        <v>-9.090909090909</v>
+        <v>-13.636363636363</v>
       </c>
       <c r="F24" s="14">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G24" s="14">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="H24" s="15">
-        <v>42.105263157894</v>
+        <v>27.272727272727</v>
       </c>
       <c r="I24" s="14">
-        <v>248</v>
+        <v>267</v>
       </c>
       <c r="J24" s="14">
-        <v>227</v>
+        <v>249</v>
       </c>
       <c r="K24" s="15">
-        <v>9.251101321585</v>
+        <v>7.228915662650</v>
       </c>
       <c r="L24" s="15">
-        <v>5.531914893617</v>
+        <v>8.536585365853</v>
       </c>
       <c r="M24" s="15">
-        <v>54.037267080745</v>
+        <v>58.928571428571</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D25" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E25" s="15">
-        <v>-16.666666666666</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="F25" s="14">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G25" s="14">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H25" s="15">
-        <v>11.764705882352</v>
+        <v>-15</v>
       </c>
       <c r="I25" s="14">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J25" s="14">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="K25" s="15">
-        <v>-7.142857142857</v>
+        <v>-15.873015873015</v>
       </c>
       <c r="L25" s="15">
-        <v>-8.771929824561</v>
+        <v>-11.666666666666</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D26" s="14">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E26" s="15">
-        <v>-30</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F26" s="14">
+        <v>50</v>
+      </c>
+      <c r="G26" s="14">
         <v>51</v>
       </c>
-      <c r="G26" s="14">
-        <v>56</v>
-      </c>
       <c r="H26" s="15">
-        <v>-8.928571428571</v>
+        <v>-1.960784313725</v>
       </c>
       <c r="I26" s="14">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="J26" s="14">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="K26" s="15">
-        <v>-6.172839506172</v>
+        <v>-8.474576271186</v>
       </c>
       <c r="L26" s="15">
-        <v>-4.402515723270</v>
+        <v>-4.705882352941</v>
       </c>
       <c r="M26" s="15">
-        <v>-14.124293785310</v>
+        <v>-12.432432432432</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,32 +1387,32 @@
       <c r="C27" s="14">
         <v>1</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
+        <v>0</v>
       </c>
       <c r="F27" s="14">
         <v>6</v>
       </c>
-      <c r="G27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H27" s="13" t="s">
-        <v>21</v>
+      <c r="G27" s="14">
+        <v>1</v>
+      </c>
+      <c r="H27" s="15">
+        <v>500</v>
       </c>
       <c r="I27" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J27" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K27" s="15">
-        <v>200</v>
+        <v>166.666666666667</v>
       </c>
       <c r="L27" s="15">
-        <v>7.142857142857</v>
+        <v>14.285714285714</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,32 +1428,32 @@
       <c r="C28" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D28" s="14">
-        <v>1</v>
-      </c>
-      <c r="E28" s="15">
-        <v>-100</v>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G28" s="14">
         <v>2</v>
       </c>
       <c r="H28" s="15">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="I28" s="14">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J28" s="14">
         <v>11</v>
       </c>
       <c r="K28" s="15">
-        <v>36.363636363636</v>
+        <v>27.272727272727</v>
       </c>
       <c r="L28" s="15">
-        <v>-6.25</v>
+        <v>-17.647058823529</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,11 +1469,11 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="14">
-        <v>1</v>
-      </c>
-      <c r="E29" s="15">
-        <v>-100</v>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F29" s="13" t="s">
         <v>20</v>
@@ -1497,10 +1497,10 @@
         <v>21</v>
       </c>
       <c r="M29" s="15">
-        <v>-85.714285714285</v>
+        <v>-87.5</v>
       </c>
       <c r="N29" s="15">
-        <v>-98.113207547169</v>
+        <v>-98.275862068965</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1510,11 +1510,11 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="14">
-        <v>1</v>
-      </c>
-      <c r="E30" s="15">
-        <v>-100</v>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F30" s="13" t="s">
         <v>20</v>
@@ -1538,10 +1538,10 @@
         <v>21</v>
       </c>
       <c r="M30" s="15">
-        <v>-83.333333333333</v>
+        <v>-85.714285714285</v>
       </c>
       <c r="N30" s="15">
-        <v>-98.113207547169</v>
+        <v>-98.245614035087</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-083pct.xlsx
+++ b/data/source/weekly/cs-en-us-083pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">15</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/30/2026</t>
+      <t xml:space="preserve">4/6/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/5/2026</t>
+      <t xml:space="preserve">4/12/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -854,26 +854,26 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>21</v>
+      <c r="D14" s="14">
+        <v>1</v>
+      </c>
+      <c r="E14" s="15">
+        <v>-100</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H14" s="13" t="s">
-        <v>21</v>
+      <c r="G14" s="14">
+        <v>1</v>
+      </c>
+      <c r="H14" s="15">
+        <v>-100</v>
       </c>
       <c r="I14" s="13" t="s">
         <v>20</v>
       </c>
       <c r="J14" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K14" s="15">
         <v>-100</v>
@@ -892,8 +892,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>1</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -902,7 +902,7 @@
         <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>20</v>
@@ -943,31 +943,31 @@
         <v>33.333333333333</v>
       </c>
       <c r="F16" s="14">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G16" s="14">
         <v>21</v>
       </c>
       <c r="H16" s="15">
-        <v>-4.761904761904</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I16" s="14">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="J16" s="14">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K16" s="15">
-        <v>60.869565217391</v>
+        <v>63.265306122449</v>
       </c>
       <c r="L16" s="15">
-        <v>-26</v>
+        <v>-25.233644859813</v>
       </c>
       <c r="M16" s="15">
-        <v>-28.846153846153</v>
+        <v>-29.203539823008</v>
       </c>
       <c r="N16" s="15">
-        <v>-80.107526881720</v>
+        <v>-79.797979797979</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D17" s="14">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E17" s="15">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="F17" s="14">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G17" s="14">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H17" s="15">
-        <v>44.444444444444</v>
+        <v>60</v>
       </c>
       <c r="I17" s="14">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="J17" s="14">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K17" s="15">
-        <v>26.966292134831</v>
+        <v>35.869565217391</v>
       </c>
       <c r="L17" s="15">
-        <v>2.727272727272</v>
+        <v>6.837606837606</v>
       </c>
       <c r="M17" s="15">
-        <v>76.5625</v>
+        <v>76.056338028169</v>
       </c>
       <c r="N17" s="15">
-        <v>-47.441860465116</v>
+        <v>-47.033898305084</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D18" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E18" s="15">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="F18" s="14">
         <v>18</v>
       </c>
       <c r="G18" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H18" s="15">
-        <v>80</v>
+        <v>38.461538461538</v>
       </c>
       <c r="I18" s="14">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="J18" s="14">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="K18" s="15">
-        <v>58.974358974359</v>
+        <v>51.162790697674</v>
       </c>
       <c r="L18" s="15">
-        <v>0</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="M18" s="15">
-        <v>-17.333333333333</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="N18" s="15">
-        <v>-81.764705882352</v>
+        <v>-82.479784366576</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D19" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E19" s="15">
-        <v>62.5</v>
+        <v>233.333333333333</v>
       </c>
       <c r="F19" s="14">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="G19" s="14">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="H19" s="15">
-        <v>75</v>
+        <v>144</v>
       </c>
       <c r="I19" s="14">
-        <v>180</v>
+        <v>197</v>
       </c>
       <c r="J19" s="14">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="K19" s="15">
-        <v>35.338345864661</v>
+        <v>41.726618705036</v>
       </c>
       <c r="L19" s="15">
-        <v>11.111111111111</v>
+        <v>15.882352941176</v>
       </c>
       <c r="M19" s="15">
-        <v>136.842105263158</v>
+        <v>143.20987654321</v>
       </c>
       <c r="N19" s="15">
-        <v>31.386861313868</v>
+        <v>40.714285714285</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
+        <v>2</v>
+      </c>
+      <c r="D20" s="14">
         <v>3</v>
       </c>
-      <c r="D20" s="14">
-        <v>2</v>
-      </c>
       <c r="E20" s="15">
-        <v>50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F20" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G20" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H20" s="15">
-        <v>-40</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="I20" s="14">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J20" s="14">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K20" s="15">
-        <v>-27.777777777777</v>
+        <v>-28.205128205128</v>
       </c>
       <c r="L20" s="15">
-        <v>-49.019607843137</v>
+        <v>-49.090909090909</v>
       </c>
       <c r="M20" s="15">
-        <v>-23.529411764705</v>
+        <v>-30</v>
       </c>
       <c r="N20" s="15">
-        <v>-90.545454545454</v>
+        <v>-90.344827586206</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D21" s="17">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E21" s="18">
-        <v>58.333333333333</v>
+        <v>110</v>
       </c>
       <c r="F21" s="17">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G21" s="17">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="H21" s="18">
-        <v>45</v>
+        <v>53.125</v>
       </c>
       <c r="I21" s="17">
-        <v>470</v>
+        <v>510</v>
       </c>
       <c r="J21" s="17">
-        <v>351</v>
+        <v>371</v>
       </c>
       <c r="K21" s="18">
-        <v>33.903133903133</v>
+        <v>37.466307277628</v>
       </c>
       <c r="L21" s="18">
-        <v>-4.858299595141</v>
+        <v>-3.409090909090</v>
       </c>
       <c r="M21" s="18">
-        <v>29.834254143646</v>
+        <v>30.102040816326</v>
       </c>
       <c r="N21" s="18">
-        <v>-65.768390386016</v>
+        <v>-65.282505105513</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="14">
+        <v>4</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1189,7 +1189,7 @@
         <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>20</v>
@@ -1198,19 +1198,19 @@
         <v>21</v>
       </c>
       <c r="I22" s="14">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="J22" s="14">
         <v>3</v>
       </c>
       <c r="K22" s="15">
-        <v>133.333333333333</v>
+        <v>300</v>
       </c>
       <c r="L22" s="15">
-        <v>-41.666666666666</v>
+        <v>0</v>
       </c>
       <c r="M22" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,8 +1220,8 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
+      <c r="C23" s="14">
+        <v>2</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>20</v>
@@ -1230,28 +1230,28 @@
         <v>21</v>
       </c>
       <c r="F23" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G23" s="14">
         <v>4</v>
       </c>
       <c r="H23" s="15">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I23" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J23" s="14">
         <v>11</v>
       </c>
       <c r="K23" s="15">
-        <v>18.181818181818</v>
+        <v>27.272727272727</v>
       </c>
       <c r="L23" s="15">
-        <v>62.5</v>
+        <v>75</v>
       </c>
       <c r="M23" s="15">
-        <v>550</v>
+        <v>366.666666666667</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="D24" s="14">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E24" s="15">
-        <v>-13.636363636363</v>
+        <v>108.333333333333</v>
       </c>
       <c r="F24" s="14">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G24" s="14">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H24" s="15">
-        <v>27.272727272727</v>
+        <v>31.884057971014</v>
       </c>
       <c r="I24" s="14">
-        <v>267</v>
+        <v>293</v>
       </c>
       <c r="J24" s="14">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="K24" s="15">
-        <v>7.228915662650</v>
+        <v>12.260536398467</v>
       </c>
       <c r="L24" s="15">
-        <v>8.536585365853</v>
+        <v>12.692307692307</v>
       </c>
       <c r="M24" s="15">
-        <v>58.928571428571</v>
+        <v>60.109289617486</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,31 +1306,31 @@
         <v>2</v>
       </c>
       <c r="D25" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E25" s="15">
-        <v>-71.428571428571</v>
+        <v>-50</v>
       </c>
       <c r="F25" s="14">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G25" s="14">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H25" s="15">
-        <v>-15</v>
+        <v>-31.818181818181</v>
       </c>
       <c r="I25" s="14">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="J25" s="14">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K25" s="15">
-        <v>-15.873015873015</v>
+        <v>-17.910447761194</v>
       </c>
       <c r="L25" s="15">
-        <v>-11.666666666666</v>
+        <v>-9.836065573770</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D26" s="14">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E26" s="15">
-        <v>-33.333333333333</v>
+        <v>-57.894736842105</v>
       </c>
       <c r="F26" s="14">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="G26" s="14">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="H26" s="15">
-        <v>-1.960784313725</v>
+        <v>-24.137931034482</v>
       </c>
       <c r="I26" s="14">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="J26" s="14">
-        <v>177</v>
+        <v>196</v>
       </c>
       <c r="K26" s="15">
-        <v>-8.474576271186</v>
+        <v>-13.775510204081</v>
       </c>
       <c r="L26" s="15">
-        <v>-4.705882352941</v>
+        <v>-5.586592178770</v>
       </c>
       <c r="M26" s="15">
-        <v>-12.432432432432</v>
+        <v>-14.213197969543</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,32 +1387,32 @@
       <c r="C27" s="14">
         <v>1</v>
       </c>
-      <c r="D27" s="14">
-        <v>1</v>
-      </c>
-      <c r="E27" s="15">
-        <v>0</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G27" s="14">
         <v>1</v>
       </c>
       <c r="H27" s="15">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="I27" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J27" s="14">
         <v>6</v>
       </c>
       <c r="K27" s="15">
-        <v>166.666666666667</v>
+        <v>183.333333333333</v>
       </c>
       <c r="L27" s="15">
-        <v>14.285714285714</v>
+        <v>21.428571428571</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1435,13 +1435,13 @@
         <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G28" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H28" s="15">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I28" s="14">
         <v>14</v>
@@ -1469,11 +1469,11 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="D29" s="14">
+        <v>1</v>
+      </c>
+      <c r="E29" s="15">
+        <v>-100</v>
       </c>
       <c r="F29" s="13" t="s">
         <v>20</v>
@@ -1488,10 +1488,10 @@
         <v>1</v>
       </c>
       <c r="J29" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K29" s="15">
-        <v>-83.333333333333</v>
+        <v>-85.714285714285</v>
       </c>
       <c r="L29" s="13" t="s">
         <v>21</v>
@@ -1500,7 +1500,7 @@
         <v>-87.5</v>
       </c>
       <c r="N29" s="15">
-        <v>-98.275862068965</v>
+        <v>-98.387096774193</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1510,11 +1510,11 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="D30" s="14">
+        <v>1</v>
+      </c>
+      <c r="E30" s="15">
+        <v>-100</v>
       </c>
       <c r="F30" s="13" t="s">
         <v>20</v>
@@ -1529,10 +1529,10 @@
         <v>1</v>
       </c>
       <c r="J30" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K30" s="15">
-        <v>-80</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="L30" s="13" t="s">
         <v>21</v>
@@ -1541,7 +1541,7 @@
         <v>-85.714285714285</v>
       </c>
       <c r="N30" s="15">
-        <v>-98.245614035087</v>
+        <v>-98.360655737704</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-083pct.xlsx
+++ b/data/source/weekly/cs-en-us-083pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">15</t>
+      <t xml:space="preserve">16</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/6/2026</t>
+      <t xml:space="preserve">4/13/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/12/2026</t>
+      <t xml:space="preserve">4/19/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -854,11 +854,11 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="14">
-        <v>1</v>
-      </c>
-      <c r="E14" s="15">
-        <v>-100</v>
+      <c r="D14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
@@ -892,8 +892,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="14">
+        <v>1</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -911,22 +911,22 @@
         <v>21</v>
       </c>
       <c r="I15" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J15" s="14">
         <v>5</v>
       </c>
       <c r="K15" s="15">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="L15" s="15">
-        <v>66.666666666666</v>
+        <v>77.777777777777</v>
       </c>
       <c r="M15" s="15">
-        <v>114.285714285714</v>
+        <v>100</v>
       </c>
       <c r="N15" s="15">
-        <v>-31.818181818181</v>
+        <v>-30.434782608695</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
+        <v>7</v>
+      </c>
+      <c r="D16" s="14">
         <v>4</v>
       </c>
-      <c r="D16" s="14">
-        <v>3</v>
-      </c>
       <c r="E16" s="15">
-        <v>33.333333333333</v>
+        <v>75</v>
       </c>
       <c r="F16" s="14">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G16" s="14">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="H16" s="15">
-        <v>-14.285714285714</v>
+        <v>75</v>
       </c>
       <c r="I16" s="14">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="J16" s="14">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="K16" s="15">
-        <v>63.265306122449</v>
+        <v>64.150943396226</v>
       </c>
       <c r="L16" s="15">
-        <v>-25.233644859813</v>
+        <v>-21.621621621621</v>
       </c>
       <c r="M16" s="15">
-        <v>-29.203539823008</v>
+        <v>-27.5</v>
       </c>
       <c r="N16" s="15">
-        <v>-79.797979797979</v>
+        <v>-79.577464788732</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D17" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E17" s="15">
-        <v>300</v>
+        <v>50</v>
       </c>
       <c r="F17" s="14">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G17" s="14">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H17" s="15">
-        <v>60</v>
+        <v>58.333333333333</v>
       </c>
       <c r="I17" s="14">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="J17" s="14">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="K17" s="15">
-        <v>35.869565217391</v>
+        <v>37.5</v>
       </c>
       <c r="L17" s="15">
-        <v>6.837606837606</v>
+        <v>4.761904761904</v>
       </c>
       <c r="M17" s="15">
-        <v>76.056338028169</v>
+        <v>55.294117647058</v>
       </c>
       <c r="N17" s="15">
-        <v>-47.033898305084</v>
+        <v>-49.425287356321</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D18" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E18" s="15">
-        <v>0</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F18" s="14">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G18" s="14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H18" s="15">
-        <v>38.461538461538</v>
+        <v>25</v>
       </c>
       <c r="I18" s="14">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J18" s="14">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K18" s="15">
-        <v>51.162790697674</v>
+        <v>39.130434782608</v>
       </c>
       <c r="L18" s="15">
-        <v>-7.142857142857</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="M18" s="15">
-        <v>-16.666666666666</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="N18" s="15">
-        <v>-82.479784366576</v>
+        <v>-84.039900249376</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D19" s="14">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E19" s="15">
-        <v>233.333333333333</v>
+        <v>25</v>
       </c>
       <c r="F19" s="14">
         <v>61</v>
       </c>
       <c r="G19" s="14">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H19" s="15">
-        <v>144</v>
+        <v>103.333333333333</v>
       </c>
       <c r="I19" s="14">
-        <v>197</v>
+        <v>214</v>
       </c>
       <c r="J19" s="14">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="K19" s="15">
-        <v>41.726618705036</v>
+        <v>41.721854304635</v>
       </c>
       <c r="L19" s="15">
-        <v>15.882352941176</v>
+        <v>16.304347826087</v>
       </c>
       <c r="M19" s="15">
-        <v>143.20987654321</v>
+        <v>140.449438202247</v>
       </c>
       <c r="N19" s="15">
-        <v>40.714285714285</v>
+        <v>39.869281045751</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D20" s="14">
         <v>3</v>
       </c>
       <c r="E20" s="15">
-        <v>-33.333333333333</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F20" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G20" s="14">
         <v>11</v>
       </c>
       <c r="H20" s="15">
-        <v>-36.363636363636</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="I20" s="14">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="J20" s="14">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K20" s="15">
-        <v>-28.205128205128</v>
+        <v>-26.190476190476</v>
       </c>
       <c r="L20" s="15">
-        <v>-49.090909090909</v>
+        <v>-46.551724137931</v>
       </c>
       <c r="M20" s="15">
-        <v>-30</v>
+        <v>-31.111111111111</v>
       </c>
       <c r="N20" s="15">
-        <v>-90.344827586206</v>
+        <v>-89.935064935064</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D21" s="17">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E21" s="18">
-        <v>110</v>
+        <v>30.769230769230</v>
       </c>
       <c r="F21" s="17">
         <v>147</v>
       </c>
       <c r="G21" s="17">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="H21" s="18">
-        <v>53.125</v>
+        <v>63.333333333333</v>
       </c>
       <c r="I21" s="17">
-        <v>510</v>
+        <v>544</v>
       </c>
       <c r="J21" s="17">
-        <v>371</v>
+        <v>397</v>
       </c>
       <c r="K21" s="18">
-        <v>37.466307277628</v>
+        <v>37.027707808564</v>
       </c>
       <c r="L21" s="18">
-        <v>-3.409090909090</v>
+        <v>-2.857142857142</v>
       </c>
       <c r="M21" s="18">
-        <v>30.102040816326</v>
+        <v>24.485125858123</v>
       </c>
       <c r="N21" s="18">
-        <v>-65.282505105513</v>
+        <v>-65.699873896595</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,7 +1180,7 @@
         <v>29</v>
       </c>
       <c r="C22" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1189,7 +1189,7 @@
         <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>20</v>
@@ -1198,19 +1198,19 @@
         <v>21</v>
       </c>
       <c r="I22" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J22" s="14">
         <v>3</v>
       </c>
       <c r="K22" s="15">
-        <v>300</v>
+        <v>366.666666666667</v>
       </c>
       <c r="L22" s="15">
-        <v>0</v>
+        <v>7.692307692307</v>
       </c>
       <c r="M22" s="15">
-        <v>50</v>
+        <v>55.555555555555</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,20 +1220,20 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="14">
+      <c r="C23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F23" s="14">
         <v>2</v>
       </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F23" s="14">
-        <v>4</v>
-      </c>
       <c r="G23" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H23" s="15">
         <v>0</v>
@@ -1248,10 +1248,10 @@
         <v>27.272727272727</v>
       </c>
       <c r="L23" s="15">
-        <v>75</v>
+        <v>55.555555555555</v>
       </c>
       <c r="M23" s="15">
-        <v>366.666666666667</v>
+        <v>180</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D24" s="14">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E24" s="15">
-        <v>108.333333333333</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F24" s="14">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G24" s="14">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="H24" s="15">
-        <v>31.884057971014</v>
+        <v>0</v>
       </c>
       <c r="I24" s="14">
-        <v>293</v>
+        <v>308</v>
       </c>
       <c r="J24" s="14">
-        <v>261</v>
+        <v>285</v>
       </c>
       <c r="K24" s="15">
-        <v>12.260536398467</v>
+        <v>8.070175438596</v>
       </c>
       <c r="L24" s="15">
-        <v>12.692307692307</v>
+        <v>10.791366906474</v>
       </c>
       <c r="M24" s="15">
-        <v>60.109289617486</v>
+        <v>51.724137931034</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,31 +1306,31 @@
         <v>2</v>
       </c>
       <c r="D25" s="14">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E25" s="15">
-        <v>-50</v>
+        <v>-80</v>
       </c>
       <c r="F25" s="14">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G25" s="14">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="H25" s="15">
-        <v>-31.818181818181</v>
+        <v>-59.259259259259</v>
       </c>
       <c r="I25" s="14">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="J25" s="14">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="K25" s="15">
-        <v>-17.910447761194</v>
+        <v>-25.974025974026</v>
       </c>
       <c r="L25" s="15">
-        <v>-9.836065573770</v>
+        <v>-13.636363636363</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D26" s="14">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E26" s="15">
-        <v>-57.894736842105</v>
+        <v>77.777777777777</v>
       </c>
       <c r="F26" s="14">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G26" s="14">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="H26" s="15">
-        <v>-24.137931034482</v>
+        <v>-24.528301886792</v>
       </c>
       <c r="I26" s="14">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="J26" s="14">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="K26" s="15">
-        <v>-13.775510204081</v>
+        <v>-9.756097560975</v>
       </c>
       <c r="L26" s="15">
-        <v>-5.586592178770</v>
+        <v>-0.537634408602</v>
       </c>
       <c r="M26" s="15">
-        <v>-14.213197969543</v>
+        <v>-11.057692307692</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1403,16 +1403,16 @@
         <v>300</v>
       </c>
       <c r="I27" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J27" s="14">
         <v>6</v>
       </c>
       <c r="K27" s="15">
-        <v>183.333333333333</v>
+        <v>200</v>
       </c>
       <c r="L27" s="15">
-        <v>21.428571428571</v>
+        <v>28.571428571428</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="C28" s="14">
+        <v>3</v>
+      </c>
+      <c r="D28" s="14">
+        <v>1</v>
+      </c>
+      <c r="E28" s="15">
+        <v>200</v>
       </c>
       <c r="F28" s="14">
+        <v>3</v>
+      </c>
+      <c r="G28" s="14">
         <v>2</v>
       </c>
-      <c r="G28" s="14">
-        <v>1</v>
-      </c>
       <c r="H28" s="15">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="I28" s="14">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J28" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K28" s="15">
-        <v>27.272727272727</v>
+        <v>41.666666666666</v>
       </c>
       <c r="L28" s="15">
-        <v>-17.647058823529</v>
+        <v>-5.555555555555</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,17 +1469,17 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="14">
-        <v>1</v>
-      </c>
-      <c r="E29" s="15">
-        <v>-100</v>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F29" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G29" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H29" s="15">
         <v>-100</v>
@@ -1497,7 +1497,7 @@
         <v>21</v>
       </c>
       <c r="M29" s="15">
-        <v>-87.5</v>
+        <v>-90</v>
       </c>
       <c r="N29" s="15">
         <v>-98.387096774193</v>
@@ -1510,17 +1510,17 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="14">
-        <v>1</v>
-      </c>
-      <c r="E30" s="15">
-        <v>-100</v>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F30" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G30" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H30" s="15">
         <v>-100</v>
@@ -1538,7 +1538,7 @@
         <v>21</v>
       </c>
       <c r="M30" s="15">
-        <v>-85.714285714285</v>
+        <v>-88.888888888888</v>
       </c>
       <c r="N30" s="15">
         <v>-98.360655737704</v>
@@ -1607,8 +1607,8 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="13" t="s">
-        <v>20</v>
+      <c r="C33" s="14">
+        <v>1</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>
@@ -1616,8 +1616,8 @@
       <c r="E33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F33" s="13" t="s">
-        <v>20</v>
+      <c r="F33" s="14">
+        <v>1</v>
       </c>
       <c r="G33" s="13" t="s">
         <v>20</v>
@@ -1625,8 +1625,8 @@
       <c r="H33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I33" s="13" t="s">
-        <v>20</v>
+      <c r="I33" s="14">
+        <v>1</v>
       </c>
       <c r="J33" s="13" t="s">
         <v>20</v>
@@ -1635,7 +1635,7 @@
         <v>21</v>
       </c>
       <c r="L33" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-083pct.xlsx
+++ b/data/source/weekly/cs-en-us-083pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">16</t>
+      <t xml:space="preserve">17</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/13/2026</t>
+      <t xml:space="preserve">4/20/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/19/2026</t>
+      <t xml:space="preserve">4/26/2026</t>
     </r>
   </si>
   <si>
@@ -851,8 +851,8 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>20</v>
+      <c r="C14" s="14">
+        <v>1</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>20</v>
@@ -860,40 +860,40 @@
       <c r="E14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="13" t="s">
-        <v>20</v>
+      <c r="F14" s="14">
+        <v>1</v>
       </c>
       <c r="G14" s="14">
         <v>1</v>
       </c>
       <c r="H14" s="15">
-        <v>-100</v>
-      </c>
-      <c r="I14" s="13" t="s">
-        <v>20</v>
+        <v>0</v>
+      </c>
+      <c r="I14" s="14">
+        <v>1</v>
       </c>
       <c r="J14" s="14">
         <v>4</v>
       </c>
       <c r="K14" s="15">
-        <v>-100</v>
+        <v>-75</v>
       </c>
       <c r="L14" s="13" t="s">
         <v>21</v>
       </c>
       <c r="M14" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="N14" s="15">
-        <v>-100</v>
+        <v>-92.857142857142</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>1</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -902,7 +902,7 @@
         <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>20</v>
@@ -920,10 +920,10 @@
         <v>220</v>
       </c>
       <c r="L15" s="15">
+        <v>60</v>
+      </c>
+      <c r="M15" s="15">
         <v>77.777777777777</v>
-      </c>
-      <c r="M15" s="15">
-        <v>100</v>
       </c>
       <c r="N15" s="15">
         <v>-30.434782608695</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D16" s="14">
         <v>4</v>
       </c>
       <c r="E16" s="15">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F16" s="14">
         <v>21</v>
       </c>
       <c r="G16" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H16" s="15">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="I16" s="14">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="J16" s="14">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="K16" s="15">
-        <v>64.150943396226</v>
+        <v>59.649122807017</v>
       </c>
       <c r="L16" s="15">
-        <v>-21.621621621621</v>
+        <v>-21.551724137931</v>
       </c>
       <c r="M16" s="15">
-        <v>-27.5</v>
+        <v>-25.409836065573</v>
       </c>
       <c r="N16" s="15">
-        <v>-79.577464788732</v>
+        <v>-79.955947136563</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,37 +978,37 @@
         <v>6</v>
       </c>
       <c r="D17" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E17" s="15">
-        <v>50</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="F17" s="14">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G17" s="14">
         <v>24</v>
       </c>
       <c r="H17" s="15">
-        <v>58.333333333333</v>
+        <v>45.833333333333</v>
       </c>
       <c r="I17" s="14">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="J17" s="14">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="K17" s="15">
-        <v>37.5</v>
+        <v>33.980582524271</v>
       </c>
       <c r="L17" s="15">
-        <v>4.761904761904</v>
+        <v>3.759398496240</v>
       </c>
       <c r="M17" s="15">
-        <v>55.294117647058</v>
+        <v>46.808510638297</v>
       </c>
       <c r="N17" s="15">
-        <v>-49.425287356321</v>
+        <v>-49.635036496350</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D18" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E18" s="15">
-        <v>-66.666666666666</v>
+        <v>50</v>
       </c>
       <c r="F18" s="14">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G18" s="14">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H18" s="15">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I18" s="14">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="J18" s="14">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K18" s="15">
-        <v>39.130434782608</v>
+        <v>39.583333333333</v>
       </c>
       <c r="L18" s="15">
-        <v>-11.111111111111</v>
+        <v>-14.102564102564</v>
       </c>
       <c r="M18" s="15">
-        <v>-27.272727272727</v>
+        <v>-27.956989247311</v>
       </c>
       <c r="N18" s="15">
-        <v>-84.039900249376</v>
+        <v>-84.382284382284</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D19" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E19" s="15">
-        <v>25</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="F19" s="14">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="G19" s="14">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="H19" s="15">
-        <v>103.333333333333</v>
+        <v>48.717948717948</v>
       </c>
       <c r="I19" s="14">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="J19" s="14">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="K19" s="15">
-        <v>41.721854304635</v>
+        <v>36.585365853658</v>
       </c>
       <c r="L19" s="15">
-        <v>16.304347826087</v>
+        <v>16.666666666666</v>
       </c>
       <c r="M19" s="15">
-        <v>140.449438202247</v>
+        <v>146.153846153846</v>
       </c>
       <c r="N19" s="15">
-        <v>39.869281045751</v>
+        <v>37.423312883435</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D20" s="14">
         <v>3</v>
       </c>
       <c r="E20" s="15">
-        <v>33.333333333333</v>
+        <v>100</v>
       </c>
       <c r="F20" s="14">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G20" s="14">
         <v>11</v>
       </c>
       <c r="H20" s="15">
-        <v>-18.181818181818</v>
+        <v>27.272727272727</v>
       </c>
       <c r="I20" s="14">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="J20" s="14">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K20" s="15">
-        <v>-26.190476190476</v>
+        <v>-17.777777777777</v>
       </c>
       <c r="L20" s="15">
-        <v>-46.551724137931</v>
+        <v>-40.322580645161</v>
       </c>
       <c r="M20" s="15">
-        <v>-31.111111111111</v>
+        <v>-19.565217391304</v>
       </c>
       <c r="N20" s="15">
-        <v>-89.935064935064</v>
+        <v>-88.544891640866</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D21" s="17">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E21" s="18">
-        <v>30.769230769230</v>
+        <v>0</v>
       </c>
       <c r="F21" s="17">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="G21" s="17">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="H21" s="18">
-        <v>63.333333333333</v>
+        <v>45.454545454545</v>
       </c>
       <c r="I21" s="17">
-        <v>544</v>
+        <v>574</v>
       </c>
       <c r="J21" s="17">
-        <v>397</v>
+        <v>426</v>
       </c>
       <c r="K21" s="18">
-        <v>37.027707808564</v>
+        <v>34.741784037558</v>
       </c>
       <c r="L21" s="18">
-        <v>-2.857142857142</v>
+        <v>-2.876480541455</v>
       </c>
       <c r="M21" s="18">
-        <v>24.485125858123</v>
+        <v>25.601750547046</v>
       </c>
       <c r="N21" s="18">
-        <v>-65.699873896595</v>
+        <v>-65.833333333333</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>2</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1232,11 +1232,11 @@
       <c r="F23" s="14">
         <v>2</v>
       </c>
-      <c r="G23" s="14">
-        <v>2</v>
-      </c>
-      <c r="H23" s="15">
-        <v>0</v>
+      <c r="G23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I23" s="14">
         <v>14</v>
@@ -1248,7 +1248,7 @@
         <v>27.272727272727</v>
       </c>
       <c r="L23" s="15">
-        <v>55.555555555555</v>
+        <v>40</v>
       </c>
       <c r="M23" s="15">
         <v>180</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D24" s="14">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E24" s="15">
-        <v>-33.333333333333</v>
+        <v>-10.526315789473</v>
       </c>
       <c r="F24" s="14">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G24" s="14">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="H24" s="15">
-        <v>0</v>
+        <v>-2.597402597402</v>
       </c>
       <c r="I24" s="14">
-        <v>308</v>
+        <v>323</v>
       </c>
       <c r="J24" s="14">
-        <v>285</v>
+        <v>304</v>
       </c>
       <c r="K24" s="15">
-        <v>8.070175438596</v>
+        <v>6.25</v>
       </c>
       <c r="L24" s="15">
-        <v>10.791366906474</v>
+        <v>7.666666666666</v>
       </c>
       <c r="M24" s="15">
-        <v>51.724137931034</v>
+        <v>49.537037037037</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D25" s="14">
+        <v>4</v>
+      </c>
+      <c r="E25" s="15">
+        <v>0</v>
+      </c>
+      <c r="F25" s="14">
         <v>10</v>
       </c>
-      <c r="E25" s="15">
-        <v>-80</v>
-      </c>
-      <c r="F25" s="14">
-        <v>11</v>
-      </c>
       <c r="G25" s="14">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H25" s="15">
-        <v>-59.259259259259</v>
+        <v>-60</v>
       </c>
       <c r="I25" s="14">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="J25" s="14">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="K25" s="15">
-        <v>-25.974025974026</v>
+        <v>-24.691358024691</v>
       </c>
       <c r="L25" s="15">
-        <v>-13.636363636363</v>
+        <v>-11.594202898550</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D26" s="14">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="E26" s="15">
-        <v>77.777777777777</v>
+        <v>-40.909090909090</v>
       </c>
       <c r="F26" s="14">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="G26" s="14">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="H26" s="15">
-        <v>-24.528301886792</v>
+        <v>-29.230769230769</v>
       </c>
       <c r="I26" s="14">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="J26" s="14">
-        <v>205</v>
+        <v>227</v>
       </c>
       <c r="K26" s="15">
-        <v>-9.756097560975</v>
+        <v>-12.775330396475</v>
       </c>
       <c r="L26" s="15">
-        <v>-0.537634408602</v>
+        <v>1.020408163265</v>
       </c>
       <c r="M26" s="15">
-        <v>-11.057692307692</v>
+        <v>-11.210762331838</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>1</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1394,13 +1394,13 @@
         <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G27" s="14">
         <v>1</v>
       </c>
       <c r="H27" s="15">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="I27" s="14">
         <v>18</v>
@@ -1412,7 +1412,7 @@
         <v>200</v>
       </c>
       <c r="L27" s="15">
-        <v>28.571428571428</v>
+        <v>20</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,22 +1426,22 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>3</v>
-      </c>
-      <c r="D28" s="14">
         <v>1</v>
       </c>
-      <c r="E28" s="15">
-        <v>200</v>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
         <v>3</v>
       </c>
       <c r="G28" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H28" s="15">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="I28" s="14">
         <v>17</v>
@@ -1453,7 +1453,7 @@
         <v>41.666666666666</v>
       </c>
       <c r="L28" s="15">
-        <v>-5.555555555555</v>
+        <v>-15</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1479,7 +1479,7 @@
         <v>20</v>
       </c>
       <c r="G29" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H29" s="15">
         <v>-100</v>
@@ -1497,10 +1497,10 @@
         <v>21</v>
       </c>
       <c r="M29" s="15">
-        <v>-90</v>
+        <v>-92.307692307692</v>
       </c>
       <c r="N29" s="15">
-        <v>-98.387096774193</v>
+        <v>-98.529411764705</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1520,7 +1520,7 @@
         <v>20</v>
       </c>
       <c r="G30" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H30" s="15">
         <v>-100</v>
@@ -1538,10 +1538,10 @@
         <v>21</v>
       </c>
       <c r="M30" s="15">
-        <v>-88.888888888888</v>
+        <v>-90</v>
       </c>
       <c r="N30" s="15">
-        <v>-98.360655737704</v>
+        <v>-98.484848484848</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1607,8 +1607,8 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="14">
-        <v>1</v>
+      <c r="C33" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-083pct.xlsx
+++ b/data/source/weekly/cs-en-us-083pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">17</t>
+      <t xml:space="preserve">18</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/20/2026</t>
+      <t xml:space="preserve">4/27/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/26/2026</t>
+      <t xml:space="preserve">5/3/2026</t>
     </r>
   </si>
   <si>
@@ -692,10 +692,10 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -851,32 +851,32 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="14">
+      <c r="C14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" s="14">
         <v>1</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>21</v>
+      <c r="E14" s="15">
+        <v>-100</v>
       </c>
       <c r="F14" s="14">
         <v>1</v>
       </c>
       <c r="G14" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H14" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I14" s="14">
         <v>1</v>
       </c>
       <c r="J14" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K14" s="15">
-        <v>-75</v>
+        <v>-80</v>
       </c>
       <c r="L14" s="13" t="s">
         <v>21</v>
@@ -885,7 +885,7 @@
         <v>-50</v>
       </c>
       <c r="N14" s="15">
-        <v>-92.857142857142</v>
+        <v>-93.333333333333</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -895,29 +895,29 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="14">
+        <v>2</v>
+      </c>
+      <c r="E15" s="15">
+        <v>-100</v>
       </c>
       <c r="F15" s="14">
+        <v>1</v>
+      </c>
+      <c r="G15" s="14">
         <v>2</v>
       </c>
-      <c r="G15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>21</v>
+      <c r="H15" s="15">
+        <v>-50</v>
       </c>
       <c r="I15" s="14">
         <v>16</v>
       </c>
       <c r="J15" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K15" s="15">
-        <v>220</v>
+        <v>128.571428571429</v>
       </c>
       <c r="L15" s="15">
         <v>60</v>
@@ -926,7 +926,7 @@
         <v>77.777777777777</v>
       </c>
       <c r="N15" s="15">
-        <v>-30.434782608695</v>
+        <v>-36</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D16" s="14">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E16" s="15">
-        <v>0</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F16" s="14">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G16" s="14">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H16" s="15">
-        <v>50</v>
+        <v>-10</v>
       </c>
       <c r="I16" s="14">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="J16" s="14">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="K16" s="15">
-        <v>59.649122807017</v>
+        <v>42.424242424242</v>
       </c>
       <c r="L16" s="15">
-        <v>-21.551724137931</v>
+        <v>-23.577235772357</v>
       </c>
       <c r="M16" s="15">
-        <v>-25.409836065573</v>
+        <v>-28.787878787878</v>
       </c>
       <c r="N16" s="15">
-        <v>-79.955947136563</v>
+        <v>-80.698151950718</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
+        <v>20</v>
+      </c>
+      <c r="D17" s="14">
         <v>6</v>
       </c>
-      <c r="D17" s="14">
-        <v>7</v>
-      </c>
       <c r="E17" s="15">
-        <v>-14.285714285714</v>
+        <v>233.333333333333</v>
       </c>
       <c r="F17" s="14">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="G17" s="14">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H17" s="15">
-        <v>45.833333333333</v>
+        <v>120</v>
       </c>
       <c r="I17" s="14">
-        <v>138</v>
+        <v>157</v>
       </c>
       <c r="J17" s="14">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="K17" s="15">
-        <v>33.980582524271</v>
+        <v>44.036697247706</v>
       </c>
       <c r="L17" s="15">
-        <v>3.759398496240</v>
+        <v>9.790209790209</v>
       </c>
       <c r="M17" s="15">
-        <v>46.808510638297</v>
+        <v>58.585858585858</v>
       </c>
       <c r="N17" s="15">
-        <v>-49.635036496350</v>
+        <v>-46.779661016949</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D18" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18" s="15">
-        <v>50</v>
+        <v>300</v>
       </c>
       <c r="F18" s="14">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G18" s="14">
         <v>10</v>
       </c>
       <c r="H18" s="15">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="I18" s="14">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="J18" s="14">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K18" s="15">
-        <v>39.583333333333</v>
+        <v>44.897959183673</v>
       </c>
       <c r="L18" s="15">
-        <v>-14.102564102564</v>
+        <v>-15.476190476190</v>
       </c>
       <c r="M18" s="15">
-        <v>-27.956989247311</v>
+        <v>-29</v>
       </c>
       <c r="N18" s="15">
-        <v>-84.382284382284</v>
+        <v>-84.009009009009</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D19" s="14">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E19" s="15">
-        <v>-30.769230769230</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="F19" s="14">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G19" s="14">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="H19" s="15">
-        <v>48.717948717948</v>
+        <v>30.952380952381</v>
       </c>
       <c r="I19" s="14">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="J19" s="14">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="K19" s="15">
-        <v>36.585365853658</v>
+        <v>33.714285714285</v>
       </c>
       <c r="L19" s="15">
-        <v>16.666666666666</v>
+        <v>12.5</v>
       </c>
       <c r="M19" s="15">
-        <v>146.153846153846</v>
+        <v>134</v>
       </c>
       <c r="N19" s="15">
-        <v>37.423312883435</v>
+        <v>31.460674157303</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D20" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E20" s="15">
-        <v>100</v>
+        <v>-80</v>
       </c>
       <c r="F20" s="14">
+        <v>13</v>
+      </c>
+      <c r="G20" s="14">
         <v>14</v>
       </c>
-      <c r="G20" s="14">
-        <v>11</v>
-      </c>
       <c r="H20" s="15">
-        <v>27.272727272727</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="I20" s="14">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J20" s="14">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="K20" s="15">
-        <v>-17.777777777777</v>
+        <v>-24</v>
       </c>
       <c r="L20" s="15">
-        <v>-40.322580645161</v>
+        <v>-40.625</v>
       </c>
       <c r="M20" s="15">
-        <v>-19.565217391304</v>
+        <v>-19.148936170212</v>
       </c>
       <c r="N20" s="15">
-        <v>-88.544891640866</v>
+        <v>-88.921282798833</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="D21" s="17">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E21" s="18">
-        <v>0</v>
+        <v>8.571428571428</v>
       </c>
       <c r="F21" s="17">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G21" s="17">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="H21" s="18">
-        <v>45.454545454545</v>
+        <v>30</v>
       </c>
       <c r="I21" s="17">
-        <v>574</v>
+        <v>611</v>
       </c>
       <c r="J21" s="17">
-        <v>426</v>
+        <v>461</v>
       </c>
       <c r="K21" s="18">
-        <v>34.741784037558</v>
+        <v>32.537960954446</v>
       </c>
       <c r="L21" s="18">
-        <v>-2.876480541455</v>
+        <v>-3.322784810126</v>
       </c>
       <c r="M21" s="18">
-        <v>25.601750547046</v>
+        <v>24.948875255623</v>
       </c>
       <c r="N21" s="18">
-        <v>-65.833333333333</v>
+        <v>-65.808617795187</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,32 +1182,32 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="D22" s="14">
+        <v>1</v>
+      </c>
+      <c r="E22" s="15">
+        <v>-100</v>
       </c>
       <c r="F22" s="14">
         <v>6</v>
       </c>
-      <c r="G22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H22" s="13" t="s">
-        <v>21</v>
+      <c r="G22" s="14">
+        <v>1</v>
+      </c>
+      <c r="H22" s="15">
+        <v>500</v>
       </c>
       <c r="I22" s="14">
         <v>14</v>
       </c>
       <c r="J22" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K22" s="15">
-        <v>366.666666666667</v>
+        <v>250</v>
       </c>
       <c r="L22" s="15">
-        <v>7.692307692307</v>
+        <v>-6.666666666666</v>
       </c>
       <c r="M22" s="15">
         <v>55.555555555555</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D24" s="14">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E24" s="15">
-        <v>-10.526315789473</v>
+        <v>-13.636363636363</v>
       </c>
       <c r="F24" s="14">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G24" s="14">
         <v>77</v>
       </c>
       <c r="H24" s="15">
-        <v>-2.597402597402</v>
+        <v>-5.194805194805</v>
       </c>
       <c r="I24" s="14">
-        <v>323</v>
+        <v>341</v>
       </c>
       <c r="J24" s="14">
-        <v>304</v>
+        <v>326</v>
       </c>
       <c r="K24" s="15">
-        <v>6.25</v>
+        <v>4.601226993865</v>
       </c>
       <c r="L24" s="15">
-        <v>7.666666666666</v>
+        <v>7.911392405063</v>
       </c>
       <c r="M24" s="15">
-        <v>49.537037037037</v>
+        <v>48.908296943231</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D25" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E25" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="F25" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G25" s="14">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H25" s="15">
-        <v>-60</v>
+        <v>-54.166666666666</v>
       </c>
       <c r="I25" s="14">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="J25" s="14">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="K25" s="15">
-        <v>-24.691358024691</v>
+        <v>-26.436781609195</v>
       </c>
       <c r="L25" s="15">
-        <v>-11.594202898550</v>
+        <v>-12.328767123287</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
+        <v>11</v>
+      </c>
+      <c r="D26" s="14">
         <v>13</v>
       </c>
-      <c r="D26" s="14">
-        <v>22</v>
-      </c>
       <c r="E26" s="15">
-        <v>-40.909090909090</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="F26" s="14">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G26" s="14">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="H26" s="15">
-        <v>-29.230769230769</v>
+        <v>-25.396825396825</v>
       </c>
       <c r="I26" s="14">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="J26" s="14">
-        <v>227</v>
+        <v>240</v>
       </c>
       <c r="K26" s="15">
-        <v>-12.775330396475</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="L26" s="15">
-        <v>1.020408163265</v>
+        <v>0</v>
       </c>
       <c r="M26" s="15">
-        <v>-11.210762331838</v>
+        <v>-12.605042016806</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,32 +1387,32 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="14">
+        <v>2</v>
+      </c>
+      <c r="E27" s="15">
+        <v>-100</v>
       </c>
       <c r="F27" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H27" s="15">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I27" s="14">
         <v>18</v>
       </c>
       <c r="J27" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K27" s="15">
-        <v>200</v>
+        <v>125</v>
       </c>
       <c r="L27" s="15">
-        <v>20</v>
+        <v>12.5</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>1</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+        <v>2</v>
+      </c>
+      <c r="D28" s="14">
+        <v>2</v>
+      </c>
+      <c r="E28" s="15">
+        <v>0</v>
       </c>
       <c r="F28" s="14">
+        <v>4</v>
+      </c>
+      <c r="G28" s="14">
         <v>3</v>
       </c>
-      <c r="G28" s="14">
-        <v>1</v>
-      </c>
       <c r="H28" s="15">
-        <v>200</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I28" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J28" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K28" s="15">
-        <v>41.666666666666</v>
+        <v>28.571428571428</v>
       </c>
       <c r="L28" s="15">
-        <v>-15</v>
+        <v>-25</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="14">
+        <v>1</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1475,40 +1475,40 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="13" t="s">
-        <v>20</v>
+      <c r="F29" s="14">
+        <v>1</v>
       </c>
       <c r="G29" s="14">
         <v>1</v>
       </c>
       <c r="H29" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J29" s="14">
         <v>7</v>
       </c>
       <c r="K29" s="15">
-        <v>-85.714285714285</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="L29" s="13" t="s">
         <v>21</v>
       </c>
       <c r="M29" s="15">
-        <v>-92.307692307692</v>
+        <v>-84.615384615384</v>
       </c>
       <c r="N29" s="15">
-        <v>-98.529411764705</v>
+        <v>-97.222222222222</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="14">
+        <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1516,32 +1516,32 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="13" t="s">
-        <v>20</v>
+      <c r="F30" s="14">
+        <v>1</v>
       </c>
       <c r="G30" s="14">
         <v>1</v>
       </c>
       <c r="H30" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J30" s="14">
         <v>6</v>
       </c>
       <c r="K30" s="15">
-        <v>-83.333333333333</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L30" s="13" t="s">
         <v>21</v>
       </c>
       <c r="M30" s="15">
-        <v>-90</v>
+        <v>-80</v>
       </c>
       <c r="N30" s="15">
-        <v>-98.484848484848</v>
+        <v>-97.142857142857</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-083pct.xlsx
+++ b/data/source/weekly/cs-en-us-083pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">18</t>
+      <t xml:space="preserve">19</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/27/2026</t>
+      <t xml:space="preserve">5/4/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">5/3/2026</t>
+      <t xml:space="preserve">5/10/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -854,20 +854,20 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="14">
-        <v>1</v>
-      </c>
-      <c r="E14" s="15">
-        <v>-100</v>
+      <c r="D14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F14" s="14">
         <v>1</v>
       </c>
       <c r="G14" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H14" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I14" s="14">
         <v>1</v>
@@ -878,14 +878,14 @@
       <c r="K14" s="15">
         <v>-80</v>
       </c>
-      <c r="L14" s="13" t="s">
-        <v>21</v>
+      <c r="L14" s="15">
+        <v>0</v>
       </c>
       <c r="M14" s="15">
         <v>-50</v>
       </c>
       <c r="N14" s="15">
-        <v>-93.333333333333</v>
+        <v>-93.75</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -895,11 +895,11 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="14">
-        <v>2</v>
-      </c>
-      <c r="E15" s="15">
-        <v>-100</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="14">
         <v>1</v>
@@ -920,13 +920,13 @@
         <v>128.571428571429</v>
       </c>
       <c r="L15" s="15">
+        <v>45.454545454545</v>
+      </c>
+      <c r="M15" s="15">
         <v>60</v>
       </c>
-      <c r="M15" s="15">
-        <v>77.777777777777</v>
-      </c>
       <c r="N15" s="15">
-        <v>-36</v>
+        <v>-42.857142857142</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D16" s="14">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E16" s="15">
-        <v>-66.666666666666</v>
+        <v>0</v>
       </c>
       <c r="F16" s="14">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G16" s="14">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H16" s="15">
-        <v>-10</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="I16" s="14">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="J16" s="14">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="K16" s="15">
-        <v>42.424242424242</v>
+        <v>40.845070422535</v>
       </c>
       <c r="L16" s="15">
-        <v>-23.577235772357</v>
+        <v>-24.812030075188</v>
       </c>
       <c r="M16" s="15">
-        <v>-28.787878787878</v>
+        <v>-29.078014184397</v>
       </c>
       <c r="N16" s="15">
-        <v>-80.698151950718</v>
+        <v>-80.769230769230</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="D17" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E17" s="15">
-        <v>233.333333333333</v>
+        <v>120</v>
       </c>
       <c r="F17" s="14">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G17" s="14">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H17" s="15">
-        <v>120</v>
+        <v>95.454545454545</v>
       </c>
       <c r="I17" s="14">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="J17" s="14">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="K17" s="15">
-        <v>44.036697247706</v>
+        <v>48.245614035087</v>
       </c>
       <c r="L17" s="15">
-        <v>9.790209790209</v>
+        <v>13.422818791946</v>
       </c>
       <c r="M17" s="15">
-        <v>58.585858585858</v>
+        <v>56.481481481481</v>
       </c>
       <c r="N17" s="15">
-        <v>-46.779661016949</v>
+        <v>-46.518987341772</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D18" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18" s="15">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="F18" s="14">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G18" s="14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H18" s="15">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="I18" s="14">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J18" s="14">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K18" s="15">
-        <v>44.897959183673</v>
+        <v>43.137254901960</v>
       </c>
       <c r="L18" s="15">
-        <v>-15.476190476190</v>
+        <v>-16.091954022988</v>
       </c>
       <c r="M18" s="15">
-        <v>-29</v>
+        <v>-33.636363636363</v>
       </c>
       <c r="N18" s="15">
-        <v>-84.009009009009</v>
+        <v>-84.267241379310</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D19" s="14">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E19" s="15">
-        <v>-9.090909090909</v>
+        <v>14.285714285714</v>
       </c>
       <c r="F19" s="14">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="G19" s="14">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="H19" s="15">
-        <v>30.952380952381</v>
+        <v>-2</v>
       </c>
       <c r="I19" s="14">
-        <v>234</v>
+        <v>249</v>
       </c>
       <c r="J19" s="14">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="K19" s="15">
-        <v>33.714285714285</v>
+        <v>31.746031746031</v>
       </c>
       <c r="L19" s="15">
-        <v>12.5</v>
+        <v>15.277777777777</v>
       </c>
       <c r="M19" s="15">
-        <v>134</v>
+        <v>137.142857142857</v>
       </c>
       <c r="N19" s="15">
-        <v>31.460674157303</v>
+        <v>31.052631578947</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D20" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E20" s="15">
-        <v>-80</v>
+        <v>0</v>
       </c>
       <c r="F20" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G20" s="14">
         <v>14</v>
       </c>
       <c r="H20" s="15">
-        <v>-7.142857142857</v>
+        <v>0</v>
       </c>
       <c r="I20" s="14">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="J20" s="14">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K20" s="15">
-        <v>-24</v>
+        <v>-22.641509433962</v>
       </c>
       <c r="L20" s="15">
-        <v>-40.625</v>
+        <v>-40.579710144927</v>
       </c>
       <c r="M20" s="15">
-        <v>-19.148936170212</v>
+        <v>-14.583333333333</v>
       </c>
       <c r="N20" s="15">
-        <v>-88.921282798833</v>
+        <v>-88.642659279778</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D21" s="17">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="E21" s="18">
-        <v>8.571428571428</v>
+        <v>27.586206896551</v>
       </c>
       <c r="F21" s="17">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="G21" s="17">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="H21" s="18">
-        <v>30</v>
+        <v>15.966386554621</v>
       </c>
       <c r="I21" s="17">
-        <v>611</v>
+        <v>649</v>
       </c>
       <c r="J21" s="17">
-        <v>461</v>
+        <v>490</v>
       </c>
       <c r="K21" s="18">
-        <v>32.537960954446</v>
+        <v>32.448979591836</v>
       </c>
       <c r="L21" s="18">
-        <v>-3.322784810126</v>
+        <v>-2.552552552552</v>
       </c>
       <c r="M21" s="18">
-        <v>24.948875255623</v>
+        <v>23.854961832061</v>
       </c>
       <c r="N21" s="18">
-        <v>-65.808617795187</v>
+        <v>-65.751978891820</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,20 +1182,20 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="14">
-        <v>1</v>
-      </c>
-      <c r="E22" s="15">
-        <v>-100</v>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G22" s="14">
         <v>1</v>
       </c>
       <c r="H22" s="15">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="I22" s="14">
         <v>14</v>
@@ -1210,7 +1210,7 @@
         <v>-6.666666666666</v>
       </c>
       <c r="M22" s="15">
-        <v>55.555555555555</v>
+        <v>40</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,8 +1220,8 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
+      <c r="C23" s="14">
+        <v>1</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>20</v>
@@ -1230,7 +1230,7 @@
         <v>21</v>
       </c>
       <c r="F23" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G23" s="13" t="s">
         <v>20</v>
@@ -1239,19 +1239,19 @@
         <v>21</v>
       </c>
       <c r="I23" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J23" s="14">
         <v>11</v>
       </c>
       <c r="K23" s="15">
-        <v>27.272727272727</v>
+        <v>36.363636363636</v>
       </c>
       <c r="L23" s="15">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="M23" s="15">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,13 +1262,13 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D24" s="14">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E24" s="15">
-        <v>-13.636363636363</v>
+        <v>91.666666666666</v>
       </c>
       <c r="F24" s="14">
         <v>73</v>
@@ -1280,19 +1280,19 @@
         <v>-5.194805194805</v>
       </c>
       <c r="I24" s="14">
-        <v>341</v>
+        <v>365</v>
       </c>
       <c r="J24" s="14">
-        <v>326</v>
+        <v>338</v>
       </c>
       <c r="K24" s="15">
-        <v>4.601226993865</v>
+        <v>7.988165680473</v>
       </c>
       <c r="L24" s="15">
-        <v>7.911392405063</v>
+        <v>9.939759036144</v>
       </c>
       <c r="M24" s="15">
-        <v>48.908296943231</v>
+        <v>51.452282157676</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D25" s="14">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E25" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="F25" s="14">
         <v>11</v>
       </c>
       <c r="G25" s="14">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H25" s="15">
-        <v>-54.166666666666</v>
+        <v>-50</v>
       </c>
       <c r="I25" s="14">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J25" s="14">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="K25" s="15">
-        <v>-26.436781609195</v>
+        <v>-25.842696629213</v>
       </c>
       <c r="L25" s="15">
-        <v>-12.328767123287</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D26" s="14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E26" s="15">
-        <v>-15.384615384615</v>
+        <v>25</v>
       </c>
       <c r="F26" s="14">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="G26" s="14">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="H26" s="15">
-        <v>-25.396825396825</v>
+        <v>-3.571428571428</v>
       </c>
       <c r="I26" s="14">
-        <v>208</v>
+        <v>223</v>
       </c>
       <c r="J26" s="14">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="K26" s="15">
-        <v>-13.333333333333</v>
+        <v>-11.507936507936</v>
       </c>
       <c r="L26" s="15">
-        <v>0</v>
+        <v>1.826484018264</v>
       </c>
       <c r="M26" s="15">
-        <v>-12.605042016806</v>
+        <v>-13.229571984435</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,20 +1387,20 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="14">
-        <v>2</v>
-      </c>
-      <c r="E27" s="15">
-        <v>-100</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G27" s="14">
         <v>2</v>
       </c>
       <c r="H27" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I27" s="14">
         <v>18</v>
@@ -1412,7 +1412,7 @@
         <v>125</v>
       </c>
       <c r="L27" s="15">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D28" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E28" s="15">
         <v>0</v>
       </c>
       <c r="F28" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G28" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H28" s="15">
-        <v>33.333333333333</v>
+        <v>16.666666666666</v>
       </c>
       <c r="I28" s="14">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J28" s="14">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K28" s="15">
-        <v>28.571428571428</v>
+        <v>23.529411764705</v>
       </c>
       <c r="L28" s="15">
-        <v>-25</v>
+        <v>-16</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>1</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1478,11 +1478,11 @@
       <c r="F29" s="14">
         <v>1</v>
       </c>
-      <c r="G29" s="14">
-        <v>1</v>
-      </c>
-      <c r="H29" s="15">
-        <v>0</v>
+      <c r="G29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I29" s="14">
         <v>2</v>
@@ -1500,15 +1500,15 @@
         <v>-84.615384615384</v>
       </c>
       <c r="N29" s="15">
-        <v>-97.222222222222</v>
+        <v>-97.260273972602</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
-        <v>1</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1519,11 +1519,11 @@
       <c r="F30" s="14">
         <v>1</v>
       </c>
-      <c r="G30" s="14">
-        <v>1</v>
-      </c>
-      <c r="H30" s="15">
-        <v>0</v>
+      <c r="G30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I30" s="14">
         <v>2</v>
@@ -1541,7 +1541,7 @@
         <v>-80</v>
       </c>
       <c r="N30" s="15">
-        <v>-97.142857142857</v>
+        <v>-97.183098591549</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1551,32 +1551,32 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="D31" s="14">
+        <v>1</v>
+      </c>
+      <c r="E31" s="15">
+        <v>-100</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H31" s="13" t="s">
-        <v>21</v>
+      <c r="G31" s="14">
+        <v>1</v>
+      </c>
+      <c r="H31" s="15">
+        <v>-100</v>
       </c>
       <c r="I31" s="14">
         <v>2</v>
       </c>
-      <c r="J31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K31" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="L31" s="13" t="s">
-        <v>21</v>
+      <c r="J31" s="14">
+        <v>1</v>
+      </c>
+      <c r="K31" s="15">
+        <v>100</v>
+      </c>
+      <c r="L31" s="15">
+        <v>100</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1635,7 +1635,7 @@
         <v>21</v>
       </c>
       <c r="L33" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>21</v>
